--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5678B53-A0FC-B74D-B254-C4CC7BA8A9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F682271B-B515-D449-ADDE-783F8B302AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10540" yWindow="-28200" windowWidth="51200" windowHeight="26580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,10 +175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TCI-SP (LSTM-HA)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(0.007)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,6 +188,66 @@
   </si>
   <si>
     <t>(0.015)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.010)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.014)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (GRU)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.022)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.017)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.021)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.027)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (Transformer)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早期即过拟合（best=9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-HA) w/o SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.005)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSTM-HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.006)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -202,7 +258,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,8 +293,15 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,8 +314,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -295,18 +364,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -317,6 +410,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -599,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -607,21 +724,21 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,392 +764,565 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="18">
         <v>0.70840000000000003</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="18">
         <v>0.15509999999999999</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="18">
         <v>0.27050000000000002</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="18">
         <v>0.44969999999999999</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="18">
         <v>0.74199999999999999</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="18">
         <v>0.75390000000000001</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="18">
         <v>0.76070000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="16"/>
+      <c r="B4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="17">
+        <v>0.70930000000000004</v>
+      </c>
+      <c r="C5" s="17">
+        <v>0.15690000000000001</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0.2732</v>
+      </c>
+      <c r="E5" s="17">
+        <v>0.45550000000000002</v>
+      </c>
+      <c r="F5" s="17">
+        <v>0.74270000000000003</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.75460000000000005</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.76160000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="16"/>
+      <c r="B6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B7" s="9">
         <v>0.71009999999999995</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C7" s="5">
         <v>0.13900000000000001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D7" s="9">
         <v>0.25919999999999999</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E7" s="9">
         <v>0.44990000000000002</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F7" s="5">
         <v>0.72130000000000005</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G7" s="9">
         <v>0.73950000000000005</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H7" s="9">
         <v>0.75149999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="8" t="s">
+    <row r="8" spans="1:9">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H8" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
+    <row r="9" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.70350000000000001</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.1396</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.73939999999999995</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.75080000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B11" s="18">
         <v>0.66169999999999995</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C11" s="18">
         <v>0.14199999999999999</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D11" s="18">
         <v>0.24110000000000001</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E11" s="18">
         <v>0.3861</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F11" s="18">
         <v>0.72860000000000003</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G11" s="18">
         <v>0.74070000000000003</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H11" s="18">
         <v>0.747</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="8" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E12" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H12" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1" t="s">
+    <row r="13" spans="1:9">
+      <c r="A13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="18">
+        <v>0.64929999999999999</v>
+      </c>
+      <c r="C13" s="18">
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0.2218</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0.35880000000000001</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B15" s="5">
         <v>0.70469999999999999</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C15" s="5">
         <v>0.14130000000000001</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D15" s="5">
         <v>0.25779999999999997</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E15" s="5">
         <v>0.44469999999999998</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F15" s="5">
         <v>0.72309999999999997</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G15" s="5">
         <v>0.74039999999999995</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H15" s="5">
         <v>0.75160000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="8" t="s">
+    <row r="16" spans="1:9">
+      <c r="B16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H16" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1">
-      <c r="A16" s="4" t="s">
+    <row r="17" spans="1:10">
+      <c r="A17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.7077</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.14729999999999999</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0.26929999999999998</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.45479999999999998</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0.72289999999999999</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0.7419</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0.75329999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="3" customFormat="1">
+      <c r="A19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="17">
+        <v>0.70120000000000005</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0.14430000000000001</v>
+      </c>
+      <c r="D19" s="18">
+        <v>0.25569999999999998</v>
+      </c>
+      <c r="E19" s="18">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0.73519999999999996</v>
+      </c>
+      <c r="G19" s="17">
+        <v>0.74709999999999999</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0.75480000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="3" customFormat="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="3" customFormat="1">
+      <c r="A21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="18">
+        <v>0.69679999999999997</v>
+      </c>
+      <c r="C21" s="18">
+        <v>0.1429</v>
+      </c>
+      <c r="D21" s="18">
+        <v>0.25419999999999998</v>
+      </c>
+      <c r="E21" s="18">
+        <v>0.42780000000000001</v>
+      </c>
+      <c r="F21" s="18">
+        <v>0.72719999999999996</v>
+      </c>
+      <c r="G21" s="18">
+        <v>0.74250000000000005</v>
+      </c>
+      <c r="H21" s="18">
+        <v>0.75160000000000005</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="3" customFormat="1">
+      <c r="A22" s="16"/>
+      <c r="B22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="3" customFormat="1">
+      <c r="A23" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="7">
-        <v>0.69679999999999997</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.1429</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0.25419999999999998</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.42780000000000001</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.72719999999999996</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.74250000000000005</v>
-      </c>
-      <c r="H16" s="7">
-        <v>0.75160000000000005</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="B23" s="18">
+        <v>0.70320000000000005</v>
+      </c>
+      <c r="C23" s="18">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0.25590000000000002</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.44209999999999999</v>
+      </c>
+      <c r="F23" s="18">
+        <v>0.71930000000000005</v>
+      </c>
+      <c r="G23" s="18">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="3" customFormat="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="8" t="s">
+    <row r="24" spans="1:10" s="3" customFormat="1">
+      <c r="A24" s="16"/>
+      <c r="B24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="3" customFormat="1">
-      <c r="A18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="7">
-        <v>0.70320000000000005</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.25590000000000002</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.44209999999999999</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.71930000000000005</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="3" customFormat="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="3" customFormat="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" s="3" customFormat="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" s="3" customFormat="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1">
       <c r="A25" s="4"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1">
       <c r="A26" s="4"/>
@@ -1045,14 +1335,14 @@
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1">
       <c r="A28" s="4"/>
@@ -1114,6 +1404,46 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
+    <row r="34" spans="1:8" s="3" customFormat="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" s="3" customFormat="1">
+      <c r="A35" s="4"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" s="3" customFormat="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" s="3" customFormat="1">
+      <c r="A37" s="4"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8814668D-0FD4-804C-8F9D-DA7A0D49DC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553AAC95-6199-A542-9511-F21D4C958DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,7 +762,7 @@
       <c r="D3" s="13">
         <v>0.37969999999999998</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>0.58399999999999996</v>
       </c>
       <c r="F3" s="12">
@@ -771,7 +771,7 @@
       <c r="G3" s="12">
         <v>0.93130000000000002</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="13">
         <v>0.92910000000000004</v>
       </c>
       <c r="I3" s="13">
@@ -846,25 +846,25 @@
         <v>18</v>
       </c>
       <c r="B5" s="12">
-        <v>0.60399999999999998</v>
+        <v>0.61350000000000005</v>
       </c>
       <c r="C5" s="12">
-        <v>0.2109</v>
+        <v>0.20930000000000001</v>
       </c>
       <c r="D5" s="12">
-        <v>0.38390000000000002</v>
-      </c>
-      <c r="E5" s="13">
-        <v>0.58379999999999999</v>
+        <v>0.39079999999999998</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.59430000000000005</v>
       </c>
       <c r="F5" s="13">
-        <v>0.92989999999999995</v>
+        <v>0.9304</v>
       </c>
       <c r="G5" s="13">
-        <v>0.93020000000000003</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0.92859999999999998</v>
+        <v>0.93089999999999995</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.92969999999999997</v>
       </c>
       <c r="I5" s="12">
         <v>0.59860000000000002</v>
@@ -891,25 +891,25 @@
     <row r="6" spans="1:15">
       <c r="A6" s="11"/>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>11</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>15</v>
@@ -1486,25 +1486,25 @@
       <c r="A19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <v>0.55689999999999995</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="13">
         <v>0.1769</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="13">
         <v>0.33739999999999998</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>0.55159999999999998</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>0.89449999999999996</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <v>0.90049999999999997</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <v>0.90459999999999996</v>
       </c>
       <c r="I19" s="12">
@@ -1580,26 +1580,26 @@
       <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="13">
-        <v>0.55330000000000001</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0.17369999999999999</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0.54710000000000003</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0.8851</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0.89459999999999995</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0.90029999999999999</v>
+      <c r="B21" s="12">
+        <v>0.56140000000000001</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0.1812</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.34010000000000001</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.55620000000000003</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.90159999999999996</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.90559999999999996</v>
       </c>
       <c r="I21" s="13">
         <v>0.53500000000000003</v>
@@ -1626,25 +1626,25 @@
     <row r="22" spans="1:15" s="3" customFormat="1">
       <c r="A22" s="11"/>
       <c r="B22" s="14" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C22" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>11</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553AAC95-6199-A542-9511-F21D4C958DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB1776D-2F9C-AF4E-B756-1B4B721A05CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,36 +61,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.007)</t>
-  </si>
-  <si>
     <t>(0.009)</t>
   </si>
   <si>
     <t>(0.008)</t>
   </si>
   <si>
-    <t>(0.013)</t>
-  </si>
-  <si>
-    <t>(0.014)</t>
-  </si>
-  <si>
-    <t>(0.006)</t>
-  </si>
-  <si>
-    <t>(0.005)</t>
-  </si>
-  <si>
     <t>(0.011)</t>
   </si>
   <si>
-    <t>(0.010)</t>
-  </si>
-  <si>
-    <t>(0.012)</t>
-  </si>
-  <si>
     <t>Transformer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,36 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.004)</t>
-  </si>
-  <si>
-    <t>(0.003)</t>
-  </si>
-  <si>
-    <t>Rec15%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rec30%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rec50%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg15%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg30%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg50%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -157,12 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.002)</t>
-  </si>
-  <si>
-    <t>(0.019)</t>
-  </si>
-  <si>
     <t>NC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,6 +117,54 @@
   </si>
   <si>
     <t>(0.016)</t>
+  </si>
+  <si>
+    <t>(0.036)</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>(0.037)</t>
+  </si>
+  <si>
+    <t>(0.023)</t>
+  </si>
+  <si>
+    <t>(0.020)</t>
+  </si>
+  <si>
+    <t>(0.022)</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>(0.028)</t>
+  </si>
+  <si>
+    <t>Rec5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rec10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rec20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -684,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -693,7 +684,7 @@
       <c r="G1" s="20"/>
       <c r="H1" s="21"/>
       <c r="I1" s="22" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
@@ -710,963 +701,459 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="C3" s="13">
-        <v>0.2082</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0.37969999999999998</v>
-      </c>
-      <c r="E3" s="13">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0.93279999999999996</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0.93130000000000002</v>
-      </c>
-      <c r="H3" s="13">
-        <v>0.92910000000000004</v>
-      </c>
-      <c r="I3" s="13">
-        <v>0.59570000000000001</v>
-      </c>
-      <c r="J3" s="13">
-        <v>0.19209999999999999</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0.36680000000000001</v>
-      </c>
-      <c r="L3" s="13">
-        <v>0.57879999999999998</v>
-      </c>
-      <c r="M3" s="13">
-        <v>0.92030000000000001</v>
-      </c>
-      <c r="N3" s="13">
-        <v>0.92090000000000005</v>
-      </c>
-      <c r="O3" s="13">
-        <v>0.92100000000000004</v>
-      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="11"/>
-      <c r="B4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="12">
-        <v>0.61350000000000005</v>
-      </c>
-      <c r="C5" s="12">
-        <v>0.20930000000000001</v>
-      </c>
-      <c r="D5" s="12">
-        <v>0.39079999999999998</v>
-      </c>
-      <c r="E5" s="12">
-        <v>0.59430000000000005</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0.9304</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.93089999999999995</v>
-      </c>
-      <c r="H5" s="12">
-        <v>0.92969999999999997</v>
-      </c>
-      <c r="I5" s="12">
-        <v>0.59860000000000002</v>
-      </c>
-      <c r="J5" s="12">
-        <v>0.1956</v>
-      </c>
-      <c r="K5" s="12">
-        <v>0.3705</v>
-      </c>
-      <c r="L5" s="12">
-        <v>0.58050000000000002</v>
-      </c>
-      <c r="M5" s="12">
-        <v>0.92759999999999998</v>
-      </c>
-      <c r="N5" s="12">
-        <v>0.92569999999999997</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0.92459999999999998</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="11"/>
-      <c r="B6" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>23</v>
-      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.60640000000000005</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.2177</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0.38879999999999998</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.58320000000000005</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.94130000000000003</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.93859999999999999</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.93479999999999996</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.57720000000000005</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.19020000000000001</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0.3569</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0.55830000000000002</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0.91979999999999995</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0.91959999999999997</v>
-      </c>
-      <c r="O7" s="5">
-        <v>0.91879999999999995</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="B8" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.61270000000000002</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.21679999999999999</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.59050000000000002</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.94320000000000004</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.93979999999999997</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.93600000000000005</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.60129999999999995</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0.37359999999999999</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.58230000000000004</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0.92490000000000006</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0.92510000000000003</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0.9244</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="B10" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>7</v>
-      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="12">
-        <v>0.58440000000000003</v>
-      </c>
-      <c r="C11" s="12">
-        <v>0.19309999999999999</v>
-      </c>
-      <c r="D11" s="12">
-        <v>0.35830000000000001</v>
-      </c>
-      <c r="E11" s="12">
-        <v>0.56820000000000004</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0.92359999999999998</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.92210000000000003</v>
-      </c>
-      <c r="H11" s="12">
-        <v>0.92079999999999995</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
       <c r="I11" s="13">
-        <v>0.56389999999999996</v>
+        <v>0.51070000000000004</v>
       </c>
       <c r="J11" s="13">
-        <v>0.17860000000000001</v>
+        <v>8.3900000000000002E-2</v>
       </c>
       <c r="K11" s="13">
-        <v>0.34360000000000002</v>
+        <v>0.13880000000000001</v>
       </c>
       <c r="L11" s="13">
-        <v>0.54749999999999999</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="M11" s="13">
-        <v>0.89229999999999998</v>
+        <v>0.63249999999999995</v>
       </c>
       <c r="N11" s="13">
-        <v>0.90059999999999996</v>
+        <v>0.65280000000000005</v>
       </c>
       <c r="O11" s="13">
-        <v>0.90469999999999995</v>
+        <v>0.66930000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="11"/>
-      <c r="B12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="16" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>14</v>
-      </c>
       <c r="K12" s="16" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0.58209999999999995</v>
-      </c>
-      <c r="C13" s="13">
-        <v>0.19159999999999999</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0.35780000000000001</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0.56640000000000001</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0.91859999999999997</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0.18440000000000001</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0.3528</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0.90149999999999997</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0.90759999999999996</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0.91039999999999999</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="11"/>
-      <c r="B14" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="16" t="s">
-        <v>11</v>
-      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="5">
-        <v>0.59060000000000001</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0.19789999999999999</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.36680000000000001</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0.57250000000000001</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.93220000000000003</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.92849999999999999</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0.92600000000000005</v>
-      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="5">
-        <v>0.5605</v>
+        <v>0.54779999999999995</v>
       </c>
       <c r="J15" s="5">
-        <v>0.17899999999999999</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K15" s="5">
-        <v>0.33860000000000001</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="L15" s="5">
-        <v>0.54210000000000003</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="M15" s="5">
-        <v>0.88849999999999996</v>
+        <v>0.71809999999999996</v>
       </c>
       <c r="N15" s="5">
-        <v>0.89770000000000005</v>
+        <v>0.7379</v>
       </c>
       <c r="O15" s="5">
-        <v>0.9022</v>
+        <v>0.75409999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="B16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="17" t="s">
         <v>6</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="6">
-        <v>0.59550000000000003</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.20039999999999999</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.372</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.92859999999999998</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.92659999999999998</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0.5766</v>
-      </c>
-      <c r="J17" s="6">
-        <v>0.18340000000000001</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0.34689999999999999</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0.55989999999999995</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0.90190000000000003</v>
-      </c>
-      <c r="N17" s="6">
-        <v>0.90700000000000003</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0.90980000000000005</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7"/>
-      <c r="B18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="O18" s="18" t="s">
-        <v>6</v>
-      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1">
       <c r="A19" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="13">
-        <v>0.55689999999999995</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0.1769</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.33739999999999998</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.55159999999999998</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.89449999999999996</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0.90049999999999997</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0.90459999999999996</v>
-      </c>
-      <c r="I19" s="12">
-        <v>0.53590000000000004</v>
-      </c>
-      <c r="J19" s="12">
-        <v>0.1628</v>
-      </c>
-      <c r="K19" s="13">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="L19" s="12">
-        <v>0.5292</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0.86160000000000003</v>
-      </c>
-      <c r="N19" s="13">
-        <v>0.87770000000000004</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0.88749999999999996</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1">
       <c r="A20" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="N20" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="O20" s="14" t="s">
-        <v>8</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" s="3" customFormat="1">
       <c r="A21" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="12">
-        <v>0.56140000000000001</v>
-      </c>
-      <c r="C21" s="12">
-        <v>0.1812</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0.34010000000000001</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0.55620000000000003</v>
-      </c>
-      <c r="F21" s="12">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.90159999999999996</v>
-      </c>
-      <c r="H21" s="12">
-        <v>0.90559999999999996</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0.16239999999999999</v>
-      </c>
-      <c r="K21" s="12">
-        <v>0.32269999999999999</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0.52690000000000003</v>
-      </c>
-      <c r="M21" s="12">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="N21" s="12">
-        <v>0.88200000000000001</v>
-      </c>
-      <c r="O21" s="12">
-        <v>0.89019999999999999</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" s="3" customFormat="1">
       <c r="A22" s="11"/>
-      <c r="B22" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>11</v>
-      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
     </row>
     <row r="23" spans="1:15" s="3" customFormat="1">
       <c r="A23" s="4"/>
@@ -1711,7 +1198,7 @@
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
-      <c r="I25" s="9"/>
+      <c r="I25" s="10"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="10"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB1776D-2F9C-AF4E-B756-1B4B721A05CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB752BB-A3D4-C64B-AFEB-49EEFF781430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,9 +122,6 @@
     <t>(0.036)</t>
   </si>
   <si>
-    <t>(0.057)</t>
-  </si>
-  <si>
     <t>(0.037)</t>
   </si>
   <si>
@@ -140,30 +137,130 @@
     <t>(0.047)</t>
   </si>
   <si>
-    <t>(0.028)</t>
-  </si>
-  <si>
-    <t>Rec5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rec10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rec20%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ndcg20%</t>
+    <t>model selection: 50% recall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.014)</t>
+  </si>
+  <si>
+    <t>(0.010)</t>
+  </si>
+  <si>
+    <t>(0.029)</t>
+  </si>
+  <si>
+    <t>(0.018)</t>
+  </si>
+  <si>
+    <t>(0.013)</t>
+  </si>
+  <si>
+    <t>(0.021)</t>
+  </si>
+  <si>
+    <t>(0.026)</t>
+  </si>
+  <si>
+    <t>(0.031)</t>
+  </si>
+  <si>
+    <t>(0.039)</t>
+  </si>
+  <si>
+    <t>(0.045)</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>(0.034)</t>
+  </si>
+  <si>
+    <t>Rec15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rec30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rec50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ndcg50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.012)</t>
+  </si>
+  <si>
+    <t>(0.024)</t>
+  </si>
+  <si>
+    <t>(0.019)</t>
+  </si>
+  <si>
+    <t>(0.006)</t>
+  </si>
+  <si>
+    <t>(0.030)</t>
+  </si>
+  <si>
+    <t>(0.027)</t>
+  </si>
+  <si>
+    <t>(0.032)</t>
+  </si>
+  <si>
+    <t>(0.033)</t>
+  </si>
+  <si>
+    <t>(0.043)</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>(0.025)</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ns=3, rho=0.99, 'partial', tai=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>h_dim=64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamb=0.01, regInv=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bs=8192, max_epoch=100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lr=0.01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -174,7 +271,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +305,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -326,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -350,9 +460,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -380,6 +487,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -662,38 +791,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
-    <col min="2" max="15" width="9" style="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="2" max="16" width="9" style="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="22" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
+      <c r="J1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="24"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="23"/>
+      <c r="R1" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,461 +833,987 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="B3" s="13">
+        <v>0.54910000000000003</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.18129999999999999</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0.34760000000000002</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.56930000000000003</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0.72460000000000002</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0.74339999999999995</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0.75719999999999998</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0.50629999999999997</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0.16650000000000001</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0.30080000000000001</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0.48520000000000002</v>
+      </c>
+      <c r="N3" s="13">
+        <v>0.6321</v>
+      </c>
+      <c r="O3" s="13">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="P3" s="13">
+        <v>0.67290000000000005</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="11"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="B4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="B5" s="12">
+        <v>0.56920000000000004</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0.37569999999999998</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.78069999999999995</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.78349999999999997</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.78520000000000001</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.53269999999999995</v>
+      </c>
+      <c r="K5" s="13">
+        <v>0.16170000000000001</v>
+      </c>
+      <c r="L5" s="13">
+        <v>0.29420000000000002</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0.54059999999999997</v>
+      </c>
+      <c r="N5" s="12">
+        <v>0.67049999999999998</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0.67749999999999999</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0.69189999999999996</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="11"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="B6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="B7" s="5">
+        <v>0.54669999999999996</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.36809999999999998</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.56510000000000005</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.75509999999999999</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.76619999999999999</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.77329999999999999</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.50349999999999995</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.16819999999999999</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.4955</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.65710000000000002</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0.66830000000000001</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0.68179999999999996</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="B8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="B9" s="6">
+        <v>0.56440000000000001</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.2339</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.3886</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.55869999999999997</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.78839999999999999</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.79139999999999999</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.7913</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.15970000000000001</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.3085</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0.55710000000000004</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.7006</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0.69869999999999999</v>
+      </c>
+      <c r="P9" s="6">
+        <v>0.70720000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="B10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13">
-        <v>0.51070000000000004</v>
-      </c>
-      <c r="J11" s="13">
-        <v>8.3900000000000002E-2</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0.13880000000000001</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0.23180000000000001</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0.63249999999999995</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0.65280000000000005</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0.66930000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="B11" s="13">
+        <v>0.51129999999999998</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.1716</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.318</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.51270000000000004</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0.67549999999999999</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.70850000000000002</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="J11" s="24">
+        <v>0.47570000000000001</v>
+      </c>
+      <c r="K11" s="24">
+        <v>0.15210000000000001</v>
+      </c>
+      <c r="L11" s="24">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="M11" s="24">
+        <v>0.4642</v>
+      </c>
+      <c r="N11" s="24">
+        <v>0.61350000000000005</v>
+      </c>
+      <c r="O11" s="24">
+        <v>0.63890000000000002</v>
+      </c>
+      <c r="P11" s="24">
+        <v>0.65969999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="11"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="16" t="s">
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="B13" s="12">
+        <v>0.5413</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.3513</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0.54679999999999995</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0.69589999999999996</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.72760000000000002</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.74380000000000002</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.5212</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0.19020000000000001</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0.3221</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0.50739999999999996</v>
+      </c>
+      <c r="N13" s="12">
+        <v>0.67930000000000001</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0.68979999999999997</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0.69820000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="11"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="B14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <v>0.54779999999999995</v>
-      </c>
-      <c r="J15" s="5">
-        <v>7.6499999999999999E-2</v>
-      </c>
-      <c r="K15" s="5">
-        <v>0.14610000000000001</v>
-      </c>
-      <c r="L15" s="5">
-        <v>0.26279999999999998</v>
-      </c>
-      <c r="M15" s="5">
-        <v>0.71809999999999996</v>
-      </c>
-      <c r="N15" s="5">
-        <v>0.7379</v>
-      </c>
-      <c r="O15" s="5">
-        <v>0.75409999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" s="17" t="s">
+      <c r="B15" s="5">
+        <v>0.55079999999999996</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.2137</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.55030000000000001</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.79549999999999998</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.79169999999999996</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.78979999999999995</v>
+      </c>
+      <c r="J15" s="28">
+        <v>0.50629999999999997</v>
+      </c>
+      <c r="K15" s="28">
+        <v>0.16650000000000001</v>
+      </c>
+      <c r="L15" s="28">
+        <v>0.30080000000000001</v>
+      </c>
+      <c r="M15" s="28">
+        <v>0.48520000000000002</v>
+      </c>
+      <c r="N15" s="28">
+        <v>0.6321</v>
+      </c>
+      <c r="O15" s="28">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="P15" s="28">
+        <v>0.67290000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="17" t="s">
+      <c r="D16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="B17" s="6">
+        <v>0.56220000000000003</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.38969999999999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.56420000000000003</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0.75619999999999998</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.76980000000000004</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="J17" s="30">
+        <v>0.49159999999999998</v>
+      </c>
+      <c r="K17" s="30">
+        <v>0.1615</v>
+      </c>
+      <c r="L17" s="30">
+        <v>0.2883</v>
+      </c>
+      <c r="M17" s="30">
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="N17" s="30">
+        <v>0.62409999999999999</v>
+      </c>
+      <c r="O17" s="30">
+        <v>0.6482</v>
+      </c>
+      <c r="P17" s="30">
+        <v>0.66559999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="7"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-    </row>
-    <row r="19" spans="1:15" s="3" customFormat="1">
+      <c r="B18" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="O18" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="3" customFormat="1">
       <c r="A19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-    </row>
-    <row r="20" spans="1:15" s="3" customFormat="1">
+      <c r="B19" s="13">
+        <v>0.52410000000000001</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0.1802</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.33550000000000002</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0.52510000000000001</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0.71940000000000004</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0.75080000000000002</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="24">
+        <v>0.48110000000000003</v>
+      </c>
+      <c r="K19" s="24">
+        <v>0.15579999999999999</v>
+      </c>
+      <c r="L19" s="24">
+        <v>0.2742</v>
+      </c>
+      <c r="M19" s="24">
+        <v>0.46439999999999998</v>
+      </c>
+      <c r="N19" s="24">
+        <v>0.61439999999999995</v>
+      </c>
+      <c r="O19" s="24">
+        <v>0.63849999999999996</v>
+      </c>
+      <c r="P19" s="24">
+        <v>0.6593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="3" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-    </row>
-    <row r="21" spans="1:15" s="3" customFormat="1">
+      <c r="B20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N20" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O20" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="3" customFormat="1">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-    </row>
-    <row r="22" spans="1:15" s="3" customFormat="1">
+      <c r="B21" s="12">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0.1787</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.33610000000000001</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.52829999999999999</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.74470000000000003</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.75449999999999995</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="24">
+        <v>0.48060000000000003</v>
+      </c>
+      <c r="K21" s="24">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="L21" s="24">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="M21" s="24">
+        <v>0.43969999999999998</v>
+      </c>
+      <c r="N21" s="24">
+        <v>0.59470000000000001</v>
+      </c>
+      <c r="O21" s="24">
+        <v>0.62009999999999998</v>
+      </c>
+      <c r="P21" s="24">
+        <v>0.64490000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="3" customFormat="1">
       <c r="A22" s="11"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-    </row>
-    <row r="23" spans="1:15" s="3" customFormat="1">
+      <c r="B22" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="3" customFormat="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1164,15 +1822,16 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-    </row>
-    <row r="24" spans="1:15" s="3" customFormat="1">
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" spans="1:16" s="3" customFormat="1">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1188,8 +1847,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" s="3" customFormat="1">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" s="3" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1199,14 +1859,15 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
-      <c r="J25" s="9"/>
+      <c r="J25" s="10"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="10"/>
+      <c r="L25" s="9"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
-    </row>
-    <row r="26" spans="1:15" s="3" customFormat="1">
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" s="3" customFormat="1">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1222,8 +1883,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" s="3" customFormat="1">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" s="3" customFormat="1">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1239,8 +1901,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" s="3" customFormat="1">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" s="3" customFormat="1">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1256,8 +1919,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" s="3" customFormat="1">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" s="3" customFormat="1">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1273,8 +1937,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" s="3" customFormat="1">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" s="3" customFormat="1">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1290,8 +1955,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" s="3" customFormat="1">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" s="3" customFormat="1">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1307,8 +1973,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" s="3" customFormat="1">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" s="3" customFormat="1">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1324,8 +1991,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" s="3" customFormat="1">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" s="3" customFormat="1">
       <c r="A33" s="4"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1341,8 +2009,9 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" s="3" customFormat="1">
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" s="3" customFormat="1">
       <c r="A34" s="4"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1358,8 +2027,9 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" s="3" customFormat="1">
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" s="3" customFormat="1">
       <c r="A35" s="4"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1375,11 +2045,12 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="J1:P1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB752BB-A3D4-C64B-AFEB-49EEFF781430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC0D088-B847-C54E-96D0-64FB1CF9C393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +137,9 @@
     <t>(0.047)</t>
   </si>
   <si>
+    <t>(0.028)</t>
+  </si>
+  <si>
     <t>model selection: 50% recall</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -261,6 +264,10 @@
   </si>
   <si>
     <t>lr=0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamb=1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -489,6 +496,9 @@
     <xf numFmtId="176" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,9 +510,6 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -821,8 +828,8 @@
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
       <c r="P1" s="23"/>
-      <c r="R1" s="27" t="s">
-        <v>60</v>
+      <c r="R1" s="28" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -833,46 +840,46 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -922,25 +929,25 @@
         <v>0.67290000000000005</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="11"/>
       <c r="B4" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>24</v>
@@ -949,7 +956,7 @@
         <v>21</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>25</v>
@@ -958,19 +965,19 @@
         <v>24</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="15" t="s">
         <v>19</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1020,16 +1027,16 @@
         <v>0.69189999999999996</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="11"/>
       <c r="B6" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>21</v>
@@ -1038,37 +1045,37 @@
         <v>21</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P6" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1118,30 +1125,30 @@
         <v>0.68179999999999996</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="B8" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>25</v>
@@ -1150,16 +1157,16 @@
         <v>20</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P8" s="16" t="s">
         <v>8</v>
@@ -1217,25 +1224,25 @@
         <v>21</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>6</v>
@@ -1244,16 +1251,16 @@
         <v>20</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1281,32 +1288,32 @@
       <c r="H11" s="13">
         <v>0.72899999999999998</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="13">
         <v>0.47570000000000001</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="13">
         <v>0.15210000000000001</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="13">
         <v>0.27700000000000002</v>
       </c>
-      <c r="M11" s="24">
+      <c r="M11" s="13">
         <v>0.4642</v>
       </c>
-      <c r="N11" s="24">
+      <c r="N11" s="13">
         <v>0.61350000000000005</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="13">
         <v>0.63890000000000002</v>
       </c>
-      <c r="P11" s="24">
+      <c r="P11" s="13">
         <v>0.65969999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="11"/>
       <c r="B12" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>19</v>
@@ -1315,36 +1322,36 @@
         <v>24</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="26" t="s">
+      <c r="J12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="N12" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="26" t="s">
+      <c r="L12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P12" s="26" t="s">
+      <c r="P12" s="15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1398,19 +1405,19 @@
     <row r="14" spans="1:18">
       <c r="A14" s="11"/>
       <c r="B14" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="15" t="s">
         <v>25</v>
@@ -1422,19 +1429,19 @@
         <v>6</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N14" s="15" t="s">
         <v>27</v>
       </c>
       <c r="O14" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P14" s="15" t="s">
         <v>24</v>
@@ -1465,25 +1472,25 @@
       <c r="H15" s="6">
         <v>0.78979999999999995</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="6">
         <v>0.50629999999999997</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="5">
         <v>0.16650000000000001</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="6">
         <v>0.30080000000000001</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="6">
         <v>0.48520000000000002</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="6">
         <v>0.6321</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="6">
         <v>0.65549999999999997</v>
       </c>
-      <c r="P15" s="28">
+      <c r="P15" s="6">
         <v>0.67290000000000005</v>
       </c>
     </row>
@@ -1501,7 +1508,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>20</v>
@@ -1509,29 +1516,29 @@
       <c r="H16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="29" t="s">
+      <c r="J16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="O16" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="P16" s="29" t="s">
+      <c r="M16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1557,43 +1564,46 @@
         <v>0.77569999999999995</v>
       </c>
       <c r="J17" s="30">
-        <v>0.49159999999999998</v>
-      </c>
-      <c r="K17" s="30">
-        <v>0.1615</v>
+        <v>0.49540000000000001</v>
+      </c>
+      <c r="K17" s="29">
+        <v>0.1668</v>
       </c>
       <c r="L17" s="30">
-        <v>0.2883</v>
+        <v>0.2959</v>
       </c>
       <c r="M17" s="30">
-        <v>0.47020000000000001</v>
+        <v>0.47089999999999999</v>
       </c>
       <c r="N17" s="30">
-        <v>0.62409999999999999</v>
+        <v>0.63019999999999998</v>
       </c>
       <c r="O17" s="30">
-        <v>0.6482</v>
+        <v>0.65290000000000004</v>
       </c>
       <c r="P17" s="30">
-        <v>0.66559999999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>0.66910000000000003</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="7"/>
       <c r="B18" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>31</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>25</v>
@@ -1602,28 +1612,28 @@
         <v>20</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K18" s="31" t="s">
         <v>50</v>
       </c>
       <c r="L18" s="31" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="O18" s="31" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="P18" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="3" customFormat="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1">
       <c r="A19" s="11" t="s">
         <v>15</v>
       </c>
@@ -1649,29 +1659,29 @@
         <v>0.75080000000000002</v>
       </c>
       <c r="I19" s="1"/>
-      <c r="J19" s="24">
+      <c r="J19" s="13">
         <v>0.48110000000000003</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="13">
         <v>0.15579999999999999</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="13">
         <v>0.2742</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="13">
         <v>0.46439999999999998</v>
       </c>
-      <c r="N19" s="24">
+      <c r="N19" s="13">
         <v>0.61439999999999995</v>
       </c>
-      <c r="O19" s="24">
+      <c r="O19" s="13">
         <v>0.63849999999999996</v>
       </c>
-      <c r="P19" s="24">
+      <c r="P19" s="13">
         <v>0.6593</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="3" customFormat="1">
+    <row r="20" spans="1:17" s="3" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>17</v>
       </c>
@@ -1685,41 +1695,41 @@
         <v>19</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="25" t="s">
+      <c r="K20" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="25" t="s">
+      <c r="L20" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="25" t="s">
+      <c r="N20" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="N20" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="3" customFormat="1">
+      <c r="P20" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -1745,75 +1755,75 @@
         <v>0.76200000000000001</v>
       </c>
       <c r="I21" s="1"/>
-      <c r="J21" s="24">
+      <c r="J21" s="25">
         <v>0.48060000000000003</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="25">
         <v>0.14499999999999999</v>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="25">
         <v>0.25109999999999999</v>
       </c>
-      <c r="M21" s="24">
+      <c r="M21" s="25">
         <v>0.43969999999999998</v>
       </c>
-      <c r="N21" s="24">
+      <c r="N21" s="25">
         <v>0.59470000000000001</v>
       </c>
-      <c r="O21" s="24">
+      <c r="O21" s="25">
         <v>0.62009999999999998</v>
       </c>
-      <c r="P21" s="24">
+      <c r="P21" s="25">
         <v>0.64490000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="3" customFormat="1">
+    <row r="22" spans="1:17" s="3" customFormat="1">
       <c r="A22" s="11"/>
       <c r="B22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="E22" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K22" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="26" t="s">
+      <c r="K22" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="26" t="s">
+      <c r="M22" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="N22" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="P22" s="26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="3" customFormat="1">
+      <c r="O22" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="3" customFormat="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1831,7 +1841,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" s="3" customFormat="1">
+    <row r="24" spans="1:17" s="3" customFormat="1">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1849,7 +1859,7 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" s="3" customFormat="1">
+    <row r="25" spans="1:17" s="3" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1867,7 +1877,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:16" s="3" customFormat="1">
+    <row r="26" spans="1:17" s="3" customFormat="1">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1885,7 +1895,7 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" s="3" customFormat="1">
+    <row r="27" spans="1:17" s="3" customFormat="1">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1903,7 +1913,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" s="3" customFormat="1">
+    <row r="28" spans="1:17" s="3" customFormat="1">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1921,7 +1931,7 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" s="3" customFormat="1">
+    <row r="29" spans="1:17" s="3" customFormat="1">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1939,7 +1949,7 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" s="3" customFormat="1">
+    <row r="30" spans="1:17" s="3" customFormat="1">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1957,7 +1967,7 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" s="3" customFormat="1">
+    <row r="31" spans="1:17" s="3" customFormat="1">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1975,7 +1985,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" s="3" customFormat="1">
+    <row r="32" spans="1:17" s="3" customFormat="1">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC0D088-B847-C54E-96D0-64FB1CF9C393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2639700-FD93-324C-9A01-AE6972D639D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="85">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,15 +61,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.009)</t>
-  </si>
-  <si>
     <t>(0.008)</t>
   </si>
   <si>
-    <t>(0.011)</t>
-  </si>
-  <si>
     <t>Transformer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -110,9 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.017)</t>
-  </si>
-  <si>
     <t>(0.015)</t>
   </si>
   <si>
@@ -128,15 +119,6 @@
     <t>(0.023)</t>
   </si>
   <si>
-    <t>(0.020)</t>
-  </si>
-  <si>
-    <t>(0.022)</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
     <t>(0.028)</t>
   </si>
   <si>
@@ -144,12 +126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.014)</t>
-  </si>
-  <si>
-    <t>(0.010)</t>
-  </si>
-  <si>
     <t>(0.029)</t>
   </si>
   <si>
@@ -207,12 +183,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(0.012)</t>
-  </si>
-  <si>
-    <t>(0.024)</t>
-  </si>
-  <si>
     <t>(0.019)</t>
   </si>
   <si>
@@ -237,9 +207,6 @@
     <t>(0.052)</t>
   </si>
   <si>
-    <t>(0.025)</t>
-  </si>
-  <si>
     <t>(0.053)</t>
   </si>
   <si>
@@ -267,8 +234,92 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lamb=1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>(0.041)</t>
+  </si>
+  <si>
+    <t>(0.076)</t>
+  </si>
+  <si>
+    <t>(0.054)</t>
+  </si>
+  <si>
+    <t>(0.050)</t>
+  </si>
+  <si>
+    <t>(0.114)</t>
+  </si>
+  <si>
+    <t>(0.074)</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>(0.102)</t>
+  </si>
+  <si>
+    <t>(0.069)</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>(0.042)</t>
+  </si>
+  <si>
+    <t>(0.044)</t>
+  </si>
+  <si>
+    <t>(0.093)</t>
+  </si>
+  <si>
+    <t>(0.077)</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>(0.071)</t>
+  </si>
+  <si>
+    <t>(0.038)</t>
+  </si>
+  <si>
+    <t>(0.083)</t>
+  </si>
+  <si>
+    <t>(0.051)</t>
+  </si>
+  <si>
+    <t>(0.062)</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>(0.040)</t>
+  </si>
+  <si>
+    <t>(0.058)</t>
+  </si>
+  <si>
+    <t>(0.073)</t>
+  </si>
+  <si>
+    <t>lr=0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.099)</t>
+  </si>
+  <si>
+    <t>(0.063)</t>
+  </si>
+  <si>
+    <t>(0.067)</t>
   </si>
 </sst>
 </file>
@@ -278,7 +329,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,13 +356,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -443,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -464,9 +508,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -499,23 +540,11 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -798,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -806,33 +835,33 @@
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="19"/>
+      <c r="J1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20"/>
-      <c r="J1" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="23"/>
-      <c r="R1" s="28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22"/>
+      <c r="S1" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -840,990 +869,993 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>40</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="13">
-        <v>0.54910000000000003</v>
+        <v>0.56040000000000001</v>
       </c>
       <c r="C3" s="13">
-        <v>0.18129999999999999</v>
+        <v>0.23549999999999999</v>
       </c>
       <c r="D3" s="13">
-        <v>0.34760000000000002</v>
+        <v>0.39889999999999998</v>
       </c>
       <c r="E3" s="13">
-        <v>0.56930000000000003</v>
+        <v>0.56769999999999998</v>
       </c>
       <c r="F3" s="13">
-        <v>0.72460000000000002</v>
+        <v>0.61129999999999995</v>
       </c>
       <c r="G3" s="13">
-        <v>0.74339999999999995</v>
+        <v>0.61719999999999997</v>
       </c>
       <c r="H3" s="13">
-        <v>0.75719999999999998</v>
+        <v>0.62470000000000003</v>
       </c>
       <c r="J3" s="13">
-        <v>0.50629999999999997</v>
-      </c>
-      <c r="K3" s="12">
-        <v>0.16650000000000001</v>
-      </c>
-      <c r="L3" s="12">
-        <v>0.30080000000000001</v>
+        <v>0.51439999999999997</v>
+      </c>
+      <c r="K3" s="13">
+        <v>0.16520000000000001</v>
+      </c>
+      <c r="L3" s="13">
+        <v>0.32700000000000001</v>
       </c>
       <c r="M3" s="13">
-        <v>0.48520000000000002</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="N3" s="13">
-        <v>0.6321</v>
+        <v>0.54249999999999998</v>
       </c>
       <c r="O3" s="13">
-        <v>0.65549999999999997</v>
+        <v>0.55579999999999996</v>
       </c>
       <c r="P3" s="13">
-        <v>0.67290000000000005</v>
-      </c>
-      <c r="R3" s="2" t="s">
+        <v>0.57179999999999997</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11"/>
+      <c r="B4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="11"/>
-      <c r="B4" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="15" t="s">
+      <c r="G4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="M4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="12">
-        <v>0.56920000000000004</v>
+        <v>0.59360000000000002</v>
       </c>
       <c r="C5" s="12">
-        <v>0.21260000000000001</v>
+        <v>0.24410000000000001</v>
       </c>
       <c r="D5" s="12">
-        <v>0.37569999999999998</v>
+        <v>0.40649999999999997</v>
       </c>
       <c r="E5" s="12">
-        <v>0.56999999999999995</v>
+        <v>0.63119999999999998</v>
       </c>
       <c r="F5" s="12">
-        <v>0.78069999999999995</v>
+        <v>0.63549999999999995</v>
       </c>
       <c r="G5" s="12">
-        <v>0.78349999999999997</v>
+        <v>0.62980000000000003</v>
       </c>
       <c r="H5" s="12">
-        <v>0.78520000000000001</v>
+        <v>0.63160000000000005</v>
       </c>
       <c r="J5" s="12">
-        <v>0.53269999999999995</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0.16170000000000001</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0.29420000000000002</v>
+        <v>0.56479999999999997</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0.20669999999999999</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0.4</v>
       </c>
       <c r="M5" s="12">
-        <v>0.54059999999999997</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="N5" s="12">
-        <v>0.67049999999999998</v>
+        <v>0.67769999999999997</v>
       </c>
       <c r="O5" s="12">
-        <v>0.67749999999999999</v>
+        <v>0.65869999999999995</v>
       </c>
       <c r="P5" s="12">
-        <v>0.69189999999999996</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>0.65449999999999997</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="11"/>
-      <c r="B6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="15" t="s">
+      <c r="D6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="F6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="5">
-        <v>0.54669999999999996</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.19600000000000001</v>
+        <v>0.57930000000000004</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.27200000000000002</v>
       </c>
       <c r="D7" s="5">
-        <v>0.36809999999999998</v>
+        <v>0.4022</v>
       </c>
       <c r="E7" s="5">
-        <v>0.56510000000000005</v>
+        <v>0.58279999999999998</v>
       </c>
       <c r="F7" s="5">
-        <v>0.75509999999999999</v>
+        <v>0.66810000000000003</v>
       </c>
       <c r="G7" s="5">
-        <v>0.76619999999999999</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="H7" s="5">
-        <v>0.77329999999999999</v>
+        <v>0.65810000000000002</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J7" s="5">
-        <v>0.50349999999999995</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0.16819999999999999</v>
+        <v>0.47439999999999999</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.13150000000000001</v>
       </c>
       <c r="L7" s="5">
-        <v>0.28299999999999997</v>
+        <v>0.2888</v>
       </c>
       <c r="M7" s="5">
-        <v>0.4955</v>
+        <v>0.48309999999999997</v>
       </c>
       <c r="N7" s="5">
-        <v>0.65710000000000002</v>
+        <v>0.4506</v>
       </c>
       <c r="O7" s="5">
-        <v>0.66830000000000001</v>
+        <v>0.48709999999999998</v>
       </c>
       <c r="P7" s="5">
-        <v>0.68179999999999996</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="B8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="16" t="s">
+        <v>0.52059999999999995</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="H8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="16" t="s">
+      <c r="L8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.60089999999999999</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.2591</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.62150000000000005</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.67569999999999997</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.66769999999999996</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.61370000000000002</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.25280000000000002</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.45619999999999999</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0.65390000000000004</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.74980000000000002</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0.71679999999999999</v>
+      </c>
+      <c r="P9" s="6">
+        <v>0.7036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="B10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.56440000000000001</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.2339</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.3886</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.55869999999999997</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.78839999999999999</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.79139999999999999</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.7913</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0.15970000000000001</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.3085</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0.55710000000000004</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0.7006</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0.69869999999999999</v>
-      </c>
-      <c r="P9" s="6">
-        <v>0.70720000000000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="B10" s="16" t="s">
+      <c r="M10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="16" t="s">
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.56340000000000001</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.20860000000000001</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.37740000000000001</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.5796</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0.61270000000000002</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.61280000000000001</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0.191</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0.34720000000000001</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0.56179999999999997</v>
+      </c>
+      <c r="N11" s="13">
+        <v>0.49830000000000002</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0.53029999999999999</v>
+      </c>
+      <c r="P11" s="13">
+        <v>0.55640000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="11"/>
+      <c r="B12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0.60680000000000001</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.25480000000000003</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0.66080000000000005</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.65629999999999999</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.65659999999999996</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.55320000000000003</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0.2011</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0.3528</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0.57079999999999997</v>
+      </c>
+      <c r="N13" s="12">
+        <v>0.53779999999999994</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0.55979999999999996</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0.57889999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="11"/>
+      <c r="B14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="L10" s="16" t="s">
+      <c r="H14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="O10" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0.51129999999999998</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0.1716</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0.318</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.51270000000000004</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0.67549999999999999</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0.70850000000000002</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0.72899999999999998</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0.47570000000000001</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0.15210000000000001</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0.27700000000000002</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0.4642</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0.61350000000000005</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0.63890000000000002</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0.65969999999999995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="11"/>
-      <c r="B12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0.5413</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0.18559999999999999</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0.3513</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0.54679999999999995</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0.69589999999999996</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.72760000000000002</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.74380000000000002</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0.5212</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0.19020000000000001</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0.3221</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0.50739999999999996</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0.67930000000000001</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0.68979999999999997</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0.69820000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="11"/>
-      <c r="B14" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="N14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="5">
-        <v>0.55079999999999996</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.2137</v>
+        <v>0.60840000000000005</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.2387</v>
       </c>
       <c r="D15" s="5">
-        <v>0.36049999999999999</v>
+        <v>0.43230000000000002</v>
       </c>
       <c r="E15" s="5">
-        <v>0.55030000000000001</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.79549999999999998</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.79169999999999996</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0.78979999999999995</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0.50629999999999997</v>
+        <v>0.62580000000000002</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.63470000000000004</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.63729999999999998</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0.5393</v>
       </c>
       <c r="K15" s="5">
-        <v>0.16650000000000001</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0.30080000000000001</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0.48520000000000002</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0.6321</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0.65549999999999997</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0.67290000000000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="B16" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="16" t="s">
+        <v>0.18090000000000001</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.32250000000000001</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.53369999999999995</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.71730000000000005</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0.69210000000000005</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0.67979999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="B16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.25159999999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.44190000000000002</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.63929999999999998</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.64139999999999997</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.64510000000000001</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.57669999999999999</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0.23930000000000001</v>
+      </c>
+      <c r="L17" s="6">
+        <v>0.39889999999999998</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0.57979999999999998</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0.76439999999999997</v>
+      </c>
+      <c r="O17" s="6">
+        <v>0.70709999999999995</v>
+      </c>
+      <c r="P17" s="6">
+        <v>0.68110000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="7"/>
+      <c r="B18" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="L18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="P16" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6">
-        <v>0.56220000000000003</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.21260000000000001</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.38969999999999999</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.56420000000000003</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.75619999999999998</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0.76980000000000004</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0.77569999999999995</v>
-      </c>
-      <c r="J17" s="30">
-        <v>0.49540000000000001</v>
-      </c>
-      <c r="K17" s="29">
-        <v>0.1668</v>
-      </c>
-      <c r="L17" s="30">
-        <v>0.2959</v>
-      </c>
-      <c r="M17" s="30">
-        <v>0.47089999999999999</v>
-      </c>
-      <c r="N17" s="30">
-        <v>0.63019999999999998</v>
-      </c>
-      <c r="O17" s="30">
-        <v>0.65290000000000004</v>
-      </c>
-      <c r="P17" s="30">
-        <v>0.66910000000000003</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="7"/>
-      <c r="B18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="L18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="O18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="P18" s="31" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="3" customFormat="1">
+      <c r="O18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="3" customFormat="1">
       <c r="A19" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="13">
-        <v>0.52410000000000001</v>
-      </c>
-      <c r="C19" s="12">
-        <v>0.1802</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.33550000000000002</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.52510000000000001</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.71940000000000004</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0.75080000000000002</v>
+        <v>0.59860000000000002</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.21940000000000001</v>
+      </c>
+      <c r="D19" s="26">
+        <v>0.40649999999999997</v>
+      </c>
+      <c r="E19" s="26">
+        <v>0.63549999999999995</v>
+      </c>
+      <c r="F19" s="26">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="G19" s="26">
+        <v>0.60780000000000001</v>
+      </c>
+      <c r="H19" s="26">
+        <v>0.6169</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="13">
-        <v>0.48110000000000003</v>
+        <v>0.55469999999999997</v>
       </c>
       <c r="K19" s="13">
-        <v>0.15579999999999999</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0.2742</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0.46439999999999998</v>
+        <v>0.18540000000000001</v>
+      </c>
+      <c r="L19" s="12">
+        <v>0.37869999999999998</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0.57750000000000001</v>
       </c>
       <c r="N19" s="13">
-        <v>0.61439999999999995</v>
+        <v>0.45440000000000003</v>
       </c>
       <c r="O19" s="13">
-        <v>0.63849999999999996</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="P19" s="13">
-        <v>0.6593</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1">
+        <v>0.54549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="3" customFormat="1">
       <c r="A20" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="P20" s="23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="3" customFormat="1">
+      <c r="A21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.6018</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0.2419</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0.40539999999999998</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0.57550000000000001</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0.6048</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="12">
+        <v>0.55310000000000004</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0.2112</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0.36070000000000002</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0.55959999999999999</v>
+      </c>
+      <c r="N21" s="12">
+        <v>0.5867</v>
+      </c>
+      <c r="O21" s="12">
+        <v>0.5927</v>
+      </c>
+      <c r="P21" s="12">
+        <v>0.60199999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="3" customFormat="1">
+      <c r="A22" s="11"/>
+      <c r="B22" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="D22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="14" t="s">
+      <c r="L22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="P22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N20" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="O20" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="P20" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="3" customFormat="1">
-      <c r="A21" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="12">
-        <v>0.53100000000000003</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0.1787</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0.33610000000000001</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0.52829999999999999</v>
-      </c>
-      <c r="F21" s="12">
-        <v>0.74470000000000003</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.75449999999999995</v>
-      </c>
-      <c r="H21" s="12">
-        <v>0.76200000000000001</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="25">
-        <v>0.48060000000000003</v>
-      </c>
-      <c r="K21" s="25">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="L21" s="25">
-        <v>0.25109999999999999</v>
-      </c>
-      <c r="M21" s="25">
-        <v>0.43969999999999998</v>
-      </c>
-      <c r="N21" s="25">
-        <v>0.59470000000000001</v>
-      </c>
-      <c r="O21" s="25">
-        <v>0.62009999999999998</v>
-      </c>
-      <c r="P21" s="25">
-        <v>0.64490000000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" s="3" customFormat="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="K22" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="L22" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="N22" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="O22" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="P22" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="3" customFormat="1">
+    </row>
+    <row r="23" spans="1:16" s="3" customFormat="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1841,7 +1873,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:17" s="3" customFormat="1">
+    <row r="24" spans="1:16" s="3" customFormat="1">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1859,15 +1891,15 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:17" s="3" customFormat="1">
+    <row r="25" spans="1:16" s="3" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="9"/>
@@ -1877,7 +1909,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:17" s="3" customFormat="1">
+    <row r="26" spans="1:16" s="3" customFormat="1">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1895,7 +1927,7 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:17" s="3" customFormat="1">
+    <row r="27" spans="1:16" s="3" customFormat="1">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1905,15 +1937,11 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:17" s="3" customFormat="1">
+    <row r="28" spans="1:16" s="3" customFormat="1">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1931,7 +1959,7 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:17" s="3" customFormat="1">
+    <row r="29" spans="1:16" s="3" customFormat="1">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1949,7 +1977,7 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:17" s="3" customFormat="1">
+    <row r="30" spans="1:16" s="3" customFormat="1">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1967,7 +1995,7 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:17" s="3" customFormat="1">
+    <row r="31" spans="1:16" s="3" customFormat="1">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1985,7 +2013,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:17" s="3" customFormat="1">
+    <row r="32" spans="1:16" s="3" customFormat="1">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2639700-FD93-324C-9A01-AE6972D639D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0161977F-07CA-D140-BA98-4CF30CEC45ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="91">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,9 +107,6 @@
     <t>(0.015)</t>
   </si>
   <si>
-    <t>(0.016)</t>
-  </si>
-  <si>
     <t>(0.036)</t>
   </si>
   <si>
@@ -320,6 +317,30 @@
   </si>
   <si>
     <t>(0.067)</t>
+  </si>
+  <si>
+    <t>raisp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.091)</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>(0.020)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.040)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.109)</t>
+  </si>
+  <si>
+    <t>(0.068)</t>
   </si>
 </sst>
 </file>
@@ -329,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,19 +375,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -487,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -519,6 +527,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -535,16 +547,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -839,26 +841,26 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
-      <c r="J1" s="20" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
+      <c r="J1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
-      <c r="S1" s="25" t="s">
-        <v>50</v>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="24"/>
+      <c r="S1" s="18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -869,46 +871,46 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="S2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -958,58 +960,58 @@
         <v>0.57179999999999997</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11"/>
       <c r="B4" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="P4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="S4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1038,10 +1040,10 @@
         <v>0.63160000000000005</v>
       </c>
       <c r="J5" s="12">
-        <v>0.56479999999999997</v>
+        <v>0.56710000000000005</v>
       </c>
       <c r="K5" s="12">
-        <v>0.20669999999999999</v>
+        <v>0.218</v>
       </c>
       <c r="L5" s="12">
         <v>0.4</v>
@@ -1059,55 +1061,55 @@
         <v>0.65449999999999997</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="11"/>
       <c r="B6" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1136,7 +1138,7 @@
         <v>0.65810000000000002</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J7" s="5">
         <v>0.47439999999999999</v>
@@ -1160,7 +1162,7 @@
         <v>0.52059999999999995</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1168,43 +1170,43 @@
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>72</v>
-      </c>
       <c r="O8" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1256,46 +1258,46 @@
     </row>
     <row r="10" spans="1:19">
       <c r="B10" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="G10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>30</v>
-      </c>
       <c r="N10" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1348,46 +1350,46 @@
     <row r="12" spans="1:19">
       <c r="A12" s="11"/>
       <c r="B12" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="G12" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="J12" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1440,46 +1442,46 @@
     <row r="14" spans="1:19">
       <c r="A14" s="11"/>
       <c r="B14" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>68</v>
-      </c>
       <c r="J14" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K14" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>20</v>
-      </c>
       <c r="N14" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1531,49 +1533,49 @@
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>28</v>
-      </c>
       <c r="K16" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O16" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P16" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1620,52 +1622,52 @@
         <v>0.68110000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:17">
       <c r="A18" s="7"/>
       <c r="B18" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="3" customFormat="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1">
       <c r="A19" s="11" t="s">
         <v>13</v>
       </c>
@@ -1675,19 +1677,19 @@
       <c r="C19" s="13">
         <v>0.21940000000000001</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="13">
         <v>0.40649999999999997</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="13">
         <v>0.63549999999999995</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="13">
         <v>0.59489999999999998</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="13">
         <v>0.60780000000000001</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="13">
         <v>0.6169</v>
       </c>
       <c r="I19" s="1"/>
@@ -1697,7 +1699,7 @@
       <c r="K19" s="13">
         <v>0.18540000000000001</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="13">
         <v>0.37869999999999998</v>
       </c>
       <c r="M19" s="12">
@@ -1713,149 +1715,152 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="3" customFormat="1">
+    <row r="20" spans="1:17" s="3" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="P20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="P20" s="23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="3" customFormat="1">
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1">
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="12">
-        <v>0.6018</v>
+        <v>0.60340000000000005</v>
       </c>
       <c r="C21" s="12">
-        <v>0.2419</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0.40539999999999998</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0.57550000000000001</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0.6048</v>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.41610000000000003</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.61009999999999998</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.61809999999999998</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.62529999999999997</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="12">
-        <v>0.55310000000000004</v>
+        <v>0.56489999999999996</v>
       </c>
       <c r="K21" s="12">
-        <v>0.2112</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0.36070000000000002</v>
+        <v>0.2034</v>
+      </c>
+      <c r="L21" s="12">
+        <v>0.3831</v>
       </c>
       <c r="M21" s="13">
-        <v>0.55959999999999999</v>
+        <v>0.56969999999999998</v>
       </c>
       <c r="N21" s="12">
-        <v>0.5867</v>
+        <v>0.60350000000000004</v>
       </c>
       <c r="O21" s="12">
-        <v>0.5927</v>
+        <v>0.61040000000000005</v>
       </c>
       <c r="P21" s="12">
-        <v>0.60199999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="3" customFormat="1">
+        <v>0.61260000000000003</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="3" customFormat="1">
       <c r="A22" s="11"/>
-      <c r="B22" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>34</v>
+      <c r="B22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="23" t="s">
-        <v>27</v>
+      <c r="J22" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="3" customFormat="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="3" customFormat="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1873,7 +1878,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" s="3" customFormat="1">
+    <row r="24" spans="1:17" s="3" customFormat="1">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1891,7 +1896,7 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" s="3" customFormat="1">
+    <row r="25" spans="1:17" s="3" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1909,7 +1914,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:16" s="3" customFormat="1">
+    <row r="26" spans="1:17" s="3" customFormat="1">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1927,7 +1932,7 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" s="3" customFormat="1">
+    <row r="27" spans="1:17" s="3" customFormat="1">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1937,11 +1942,15 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="10"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" s="3" customFormat="1">
+    <row r="28" spans="1:17" s="3" customFormat="1">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1959,7 +1968,7 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" s="3" customFormat="1">
+    <row r="29" spans="1:17" s="3" customFormat="1">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1977,7 +1986,7 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" s="3" customFormat="1">
+    <row r="30" spans="1:17" s="3" customFormat="1">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1995,7 +2004,7 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" s="3" customFormat="1">
+    <row r="31" spans="1:17" s="3" customFormat="1">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2013,7 +2022,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" s="3" customFormat="1">
+    <row r="32" spans="1:17" s="3" customFormat="1">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0161977F-07CA-D140-BA98-4CF30CEC45ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B63F184-E8FA-644F-AABA-9AE0DF67F39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="134">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,9 +255,6 @@
     <t>(0.035)</t>
   </si>
   <si>
-    <t>(0.102)</t>
-  </si>
-  <si>
     <t>(0.069)</t>
   </si>
   <si>
@@ -341,6 +338,179 @@
   </si>
   <si>
     <t>(0.068)</t>
+  </si>
+  <si>
+    <t>Ali</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.005)</t>
+  </si>
+  <si>
+    <t>(0.010)</t>
+  </si>
+  <si>
+    <t>(0.007)</t>
+  </si>
+  <si>
+    <t>(0.045)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.017)</t>
+  </si>
+  <si>
+    <t>(0.017)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.015)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.014)</t>
+  </si>
+  <si>
+    <t>(0.004)</t>
+  </si>
+  <si>
+    <t>(0.009)</t>
+  </si>
+  <si>
+    <t>(0.016)</t>
+  </si>
+  <si>
+    <t>(0.021)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.016)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.012)</t>
+  </si>
+  <si>
+    <t>(0.003)</t>
+  </si>
+  <si>
+    <t>(0.011)</t>
+  </si>
+  <si>
+    <t>(0.020)</t>
+  </si>
+  <si>
+    <t>(0.022)</t>
+  </si>
+  <si>
+    <t>(0.013)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamb=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.011)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.006)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train: 240301-240509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>val: 240510-240512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test: 240513-240515</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LSTM-Tatt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamb=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.023)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.019)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.022)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.025)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.029)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.026)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>(0.066)</t>
+  </si>
+  <si>
+    <t>83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>horizon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>太久，风格可能也会变化</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -350,7 +520,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,8 +548,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +584,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -508,7 +691,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -549,6 +731,19 @@
     <xf numFmtId="176" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -829,41 +1024,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
     <col min="2" max="16" width="9" style="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="17" max="17" width="9" style="2"/>
+    <col min="18" max="24" width="9" style="1"/>
+    <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21"/>
-      <c r="J1" s="22" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
+      <c r="J1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="24"/>
-      <c r="S1" s="18" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="23"/>
+      <c r="R1" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="26"/>
+      <c r="Z1" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,210 +1115,315 @@
       <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="R2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:26">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>0.56040000000000001</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>0.23549999999999999</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>0.39889999999999998</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>0.56769999999999998</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>0.61129999999999995</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>0.61719999999999997</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>0.62470000000000003</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <v>0.51439999999999997</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>0.16520000000000001</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <v>0.32700000000000001</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <v>0.52700000000000002</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="12">
         <v>0.54249999999999998</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="12">
         <v>0.55579999999999996</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="12">
         <v>0.57179999999999997</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0.50580000000000003</v>
+      </c>
+      <c r="S3" s="12">
+        <v>0.19220000000000001</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0.36020000000000002</v>
+      </c>
+      <c r="U3" s="12">
+        <v>0.57509999999999994</v>
+      </c>
+      <c r="V3" s="12">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="W3" s="12">
+        <v>0.75119999999999998</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0.75780000000000003</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="10"/>
+      <c r="B4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="11"/>
-      <c r="B4" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="O4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="X4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.59360000000000002</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.40649999999999997</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.63119999999999998</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.63549999999999995</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.62980000000000003</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.63160000000000005</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0.56710000000000005</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.218</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="M5" s="11">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.67769999999999997</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0.65869999999999995</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0.65449999999999997</v>
+      </c>
+      <c r="R5" s="11">
+        <v>0.59740000000000004</v>
+      </c>
+      <c r="S5" s="11">
+        <v>0.2394</v>
+      </c>
+      <c r="T5" s="11">
+        <v>0.42920000000000003</v>
+      </c>
+      <c r="U5" s="11">
+        <v>0.64639999999999997</v>
+      </c>
+      <c r="V5" s="11">
+        <v>0.75509999999999999</v>
+      </c>
+      <c r="W5" s="11">
+        <v>0.76939999999999997</v>
+      </c>
+      <c r="X5" s="11">
+        <v>0.77639999999999998</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="10"/>
+      <c r="B6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="14" t="s">
+      <c r="C6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="12">
-        <v>0.59360000000000002</v>
-      </c>
-      <c r="C5" s="12">
-        <v>0.24410000000000001</v>
-      </c>
-      <c r="D5" s="12">
-        <v>0.40649999999999997</v>
-      </c>
-      <c r="E5" s="12">
-        <v>0.63119999999999998</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.63549999999999995</v>
-      </c>
-      <c r="G5" s="12">
-        <v>0.62980000000000003</v>
-      </c>
-      <c r="H5" s="12">
-        <v>0.63160000000000005</v>
-      </c>
-      <c r="J5" s="12">
-        <v>0.56710000000000005</v>
-      </c>
-      <c r="K5" s="12">
-        <v>0.218</v>
-      </c>
-      <c r="L5" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="M5" s="12">
-        <v>0.58199999999999996</v>
-      </c>
-      <c r="N5" s="12">
-        <v>0.67769999999999997</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0.65869999999999995</v>
-      </c>
-      <c r="P5" s="12">
-        <v>0.65449999999999997</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="11"/>
-      <c r="B6" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="14" t="s">
+      <c r="O6" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="P6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="2" t="s">
+      <c r="P6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="V6" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z6" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:26">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1138,7 +1449,7 @@
         <v>0.65810000000000002</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" s="5">
         <v>0.47439999999999999</v>
@@ -1161,55 +1472,97 @@
       <c r="P7" s="5">
         <v>0.52059999999999995</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="R7" s="5">
+        <v>0.53490000000000004</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0.2122</v>
+      </c>
+      <c r="T7" s="5">
+        <v>0.40450000000000003</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0.61450000000000005</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0.72270000000000001</v>
+      </c>
+      <c r="W7" s="5">
+        <v>0.74039999999999995</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0.75390000000000001</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:26">
+      <c r="B8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="R8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1255,236 +1608,371 @@
       <c r="P9" s="6">
         <v>0.7036</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="B10" s="15" t="s">
+      <c r="R9" s="6">
+        <v>0.59279999999999999</v>
+      </c>
+      <c r="S9" s="6">
+        <v>0.2427</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0.42430000000000001</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0.64439999999999997</v>
+      </c>
+      <c r="V9" s="6">
+        <v>0.74419999999999997</v>
+      </c>
+      <c r="W9" s="6">
+        <v>0.76229999999999998</v>
+      </c>
+      <c r="X9" s="6">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="B10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="G10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="X10" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0.56340000000000001</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.20860000000000001</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0.37740000000000001</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.5796</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0.61270000000000002</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.61280000000000001</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="K11" s="12">
+        <v>0.191</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0.34720000000000001</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0.56179999999999997</v>
+      </c>
+      <c r="N11" s="12">
+        <v>0.49830000000000002</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0.53029999999999999</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0.55640000000000001</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0.57920000000000005</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0.20280000000000001</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0.39410000000000001</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0.61980000000000002</v>
+      </c>
+      <c r="V11" s="12">
+        <v>0.73050000000000004</v>
+      </c>
+      <c r="W11" s="12">
+        <v>0.75160000000000005</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0.7631</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="10"/>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="15" t="s">
+      <c r="F12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="U12" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="X12" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="11">
+        <v>0.60680000000000001</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.25480000000000003</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0.66080000000000005</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.65629999999999999</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.65659999999999996</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.55320000000000003</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0.2011</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0.3528</v>
+      </c>
+      <c r="M13" s="11">
+        <v>0.57079999999999997</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.53779999999999994</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0.55979999999999996</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0.57889999999999997</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0.59189999999999998</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0.4249</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0.63649999999999995</v>
+      </c>
+      <c r="V13" s="11">
+        <v>0.74860000000000004</v>
+      </c>
+      <c r="W13" s="11">
+        <v>0.76529999999999998</v>
+      </c>
+      <c r="X13" s="11">
+        <v>0.77310000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="10"/>
+      <c r="B14" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0.56340000000000001</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0.20860000000000001</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0.37740000000000001</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.5796</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0.61270000000000002</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0.61280000000000001</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0.61919999999999997</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0.54749999999999999</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0.191</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0.34720000000000001</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0.56179999999999997</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0.49830000000000002</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0.53029999999999999</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0.55640000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" s="11"/>
-      <c r="B12" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="14" t="s">
+      <c r="H14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="O12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="P12" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0.60680000000000001</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0.25480000000000003</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0.44409999999999999</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0.63439999999999996</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0.66080000000000005</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.65629999999999999</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0.55320000000000003</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0.2011</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0.3528</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0.57079999999999997</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0.53779999999999994</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0.55979999999999996</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0.57889999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="11"/>
-      <c r="B14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="14" t="s">
+      <c r="R14" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="S14" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="T14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="U14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="X14" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -1530,75 +2018,120 @@
       <c r="P15" s="5">
         <v>0.67979999999999996</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="B16" s="15" t="s">
+      <c r="R15" s="5">
+        <v>0.59379999999999999</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0.21659999999999999</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0.42049999999999998</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0.73819999999999997</v>
+      </c>
+      <c r="W15" s="5">
+        <v>0.75219999999999998</v>
+      </c>
+      <c r="X15" s="5">
+        <v>0.76060000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="B16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" s="15" t="s">
+      <c r="D16" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M16" s="15" t="s">
+      <c r="M16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="N16" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="O16" s="15" t="s">
+      <c r="N16" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="P16" s="15" t="s">
+      <c r="O16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" s="14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="V16" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="W16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="X16" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>0.62439999999999996</v>
+        <v>0.62370000000000003</v>
       </c>
       <c r="C17" s="6">
-        <v>0.25159999999999999</v>
+        <v>0.27960000000000002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.44190000000000002</v>
+        <v>0.45050000000000001</v>
       </c>
       <c r="E17" s="6">
-        <v>0.66669999999999996</v>
+        <v>0.64729999999999999</v>
       </c>
       <c r="F17" s="6">
-        <v>0.63929999999999998</v>
+        <v>0.64880000000000004</v>
       </c>
       <c r="G17" s="6">
-        <v>0.64139999999999997</v>
+        <v>0.6492</v>
       </c>
       <c r="H17" s="6">
-        <v>0.64510000000000001</v>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J17" s="6">
         <v>0.57669999999999999</v>
@@ -1621,246 +2154,378 @@
       <c r="P17" s="6">
         <v>0.68110000000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="6">
+        <v>0.59930000000000005</v>
+      </c>
+      <c r="S17" s="6">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="T17" s="6">
+        <v>0.43309999999999998</v>
+      </c>
+      <c r="U17" s="6">
+        <v>0.66069999999999995</v>
+      </c>
+      <c r="V17" s="6">
+        <v>0.75239999999999996</v>
+      </c>
+      <c r="W17" s="6">
+        <v>0.75480000000000003</v>
+      </c>
+      <c r="X17" s="6">
+        <v>0.76859999999999995</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="7"/>
-      <c r="B18" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="16" t="s">
+      <c r="P18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="S18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="T18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="U18" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="V18" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="W18" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="X18" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" s="3" customFormat="1">
+      <c r="A19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="12">
+        <v>0.59860000000000002</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0.21940000000000001</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0.40649999999999997</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0.63549999999999995</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.60780000000000001</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.6169</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="12">
+        <v>0.55469999999999997</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0.18540000000000001</v>
+      </c>
+      <c r="L19" s="12">
+        <v>0.37869999999999998</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0.57750000000000001</v>
+      </c>
+      <c r="N19" s="12">
+        <v>0.45440000000000003</v>
+      </c>
+      <c r="O19" s="12">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="P19" s="12">
+        <v>0.54549999999999998</v>
+      </c>
+      <c r="R19" s="12">
+        <v>0.59089999999999998</v>
+      </c>
+      <c r="S19" s="12">
+        <v>0.21590000000000001</v>
+      </c>
+      <c r="T19" s="12">
+        <v>0.41489999999999999</v>
+      </c>
+      <c r="U19" s="12">
+        <v>0.64349999999999996</v>
+      </c>
+      <c r="V19" s="12">
+        <v>0.73219999999999996</v>
+      </c>
+      <c r="W19" s="12">
+        <v>0.74980000000000002</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0.76219999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" s="3" customFormat="1">
+      <c r="A20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="O20" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="O18" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="P18" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="3" customFormat="1">
-      <c r="A19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="13">
-        <v>0.59860000000000002</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0.21940000000000001</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.40649999999999997</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.63549999999999995</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.59489999999999998</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0.60780000000000001</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0.6169</v>
-      </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="13">
-        <v>0.55469999999999997</v>
-      </c>
-      <c r="K19" s="13">
-        <v>0.18540000000000001</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0.37869999999999998</v>
-      </c>
-      <c r="M19" s="12">
-        <v>0.57750000000000001</v>
-      </c>
-      <c r="N19" s="13">
-        <v>0.45440000000000003</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="P19" s="13">
-        <v>0.54549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1">
-      <c r="A20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="P20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="S20" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="W20" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="X20" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" s="3" customFormat="1">
+      <c r="A21" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="11">
+        <v>0.60340000000000005</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0.41610000000000003</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0.61009999999999998</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.61809999999999998</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.62529999999999997</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="11">
+        <v>0.56489999999999996</v>
+      </c>
+      <c r="K21" s="11">
+        <v>0.2034</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0.3831</v>
+      </c>
+      <c r="M21" s="12">
+        <v>0.56969999999999998</v>
+      </c>
+      <c r="N21" s="11">
+        <v>0.60350000000000004</v>
+      </c>
+      <c r="O21" s="11">
+        <v>0.61040000000000005</v>
+      </c>
+      <c r="P21" s="11">
+        <v>0.61260000000000003</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R21" s="11">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="S21" s="11">
+        <v>0.2225</v>
+      </c>
+      <c r="T21" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="U21" s="11">
+        <v>0.6542</v>
+      </c>
+      <c r="V21" s="11">
+        <v>0.74509999999999998</v>
+      </c>
+      <c r="W21" s="11">
+        <v>0.76119999999999999</v>
+      </c>
+      <c r="X21" s="11">
+        <v>0.77290000000000003</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" s="3" customFormat="1">
+      <c r="A22" s="10"/>
+      <c r="B22" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="L22" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="3" customFormat="1">
-      <c r="A21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="12">
-        <v>0.60340000000000005</v>
-      </c>
-      <c r="C21" s="12">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0.41610000000000003</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0.64410000000000001</v>
-      </c>
-      <c r="F21" s="12">
-        <v>0.61009999999999998</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.61809999999999998</v>
-      </c>
-      <c r="H21" s="12">
-        <v>0.62529999999999997</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="12">
-        <v>0.56489999999999996</v>
-      </c>
-      <c r="K21" s="12">
-        <v>0.2034</v>
-      </c>
-      <c r="L21" s="12">
-        <v>0.3831</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0.56969999999999998</v>
-      </c>
-      <c r="N21" s="12">
-        <v>0.60350000000000004</v>
-      </c>
-      <c r="O21" s="12">
-        <v>0.61040000000000005</v>
-      </c>
-      <c r="P21" s="12">
-        <v>0.61260000000000003</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" s="3" customFormat="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="14" t="s">
+      <c r="M22" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="M22" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="N22" s="14" t="s">
+      <c r="N22" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="O22" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="P22" s="14" t="s">
+      <c r="P22" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" s="3" customFormat="1">
+      <c r="R22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="S22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="T22" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="V22" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="X22" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" s="3" customFormat="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1877,8 +2542,15 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
-    </row>
-    <row r="24" spans="1:17" s="3" customFormat="1">
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+    </row>
+    <row r="24" spans="1:25" s="3" customFormat="1">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1895,34 +2567,58 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:17" s="3" customFormat="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-    </row>
-    <row r="26" spans="1:17" s="3" customFormat="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+    </row>
+    <row r="25" spans="1:25" s="3" customFormat="1">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+    </row>
+    <row r="26" spans="1:25" s="3" customFormat="1">
+      <c r="A26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="12">
+        <v>0.57450000000000001</v>
+      </c>
+      <c r="C26" s="11">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="D26" s="12">
+        <v>0.38529999999999998</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0.5706</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1931,34 +2627,68 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:17" s="3" customFormat="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+    </row>
+    <row r="27" spans="1:25" s="3" customFormat="1">
+      <c r="A27" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="10"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="9"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:17" s="3" customFormat="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+    </row>
+    <row r="28" spans="1:25" s="3" customFormat="1">
+      <c r="A28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="11">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="C28" s="12">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="D28" s="11">
+        <v>0.4118</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0.60289999999999999</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1967,16 +2697,33 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:17" s="3" customFormat="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+    </row>
+    <row r="29" spans="1:25" s="3" customFormat="1">
+      <c r="A29" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1985,16 +2732,33 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:17" s="3" customFormat="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+    </row>
+    <row r="30" spans="1:25" s="3" customFormat="1">
+      <c r="A30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="5">
+        <v>0.59040000000000004</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0.41880000000000001</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.61560000000000004</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2003,16 +2767,33 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:17" s="3" customFormat="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+    </row>
+    <row r="31" spans="1:25" s="3" customFormat="1">
+      <c r="A31" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2021,16 +2802,33 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:17" s="3" customFormat="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:25" s="3" customFormat="1">
+      <c r="A32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6">
+        <v>0.60450000000000004</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.24840000000000001</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.61880000000000002</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2039,16 +2837,33 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" s="3" customFormat="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24" s="3" customFormat="1">
+      <c r="A33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2057,16 +2872,33 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16" s="3" customFormat="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24" s="3" customFormat="1">
+      <c r="A34" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="12">
+        <v>0.60840000000000005</v>
+      </c>
+      <c r="C34" s="12">
+        <v>0.2387</v>
+      </c>
+      <c r="D34" s="12">
+        <v>0.43230000000000002</v>
+      </c>
+      <c r="E34" s="12">
+        <v>0.62580000000000002</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2075,16 +2907,33 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" s="3" customFormat="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24" s="3" customFormat="1">
+      <c r="A35" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2093,11 +2942,391 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="1:24">
+      <c r="A36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="11">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D36" s="11">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:24">
+      <c r="A37" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:24">
+      <c r="A38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="5">
+        <v>0.59119999999999995</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.2082</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0.60329999999999995</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="A39" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:24">
+      <c r="A40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="6">
+        <v>0.60209999999999997</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.2283</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:24">
+      <c r="A41" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:24">
+      <c r="A42" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="12">
+        <v>0.58909999999999996</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="D42" s="12">
+        <v>0.4032</v>
+      </c>
+      <c r="E42" s="12">
+        <v>0.60719999999999996</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:24">
+      <c r="A43" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:24">
+      <c r="A44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="11">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="C44" s="12">
+        <v>0.21160000000000001</v>
+      </c>
+      <c r="D44" s="11">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="E44" s="11">
+        <v>0.63370000000000004</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:24">
+      <c r="A45" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:24">
+      <c r="A46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="5">
+        <v>0.59130000000000005</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="D46" s="5">
+        <v>0.40150000000000002</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.6179</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:24">
+      <c r="A48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="6">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="C48" s="5">
+        <v>0.2094</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.63580000000000003</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="12">
+        <v>0.59140000000000004</v>
+      </c>
+      <c r="C50" s="11">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="E50" s="12">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="11">
+        <v>0.58919999999999995</v>
+      </c>
+      <c r="C52" s="12">
+        <v>0.2041</v>
+      </c>
+      <c r="D52" s="12">
+        <v>0.39169999999999999</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0.62880000000000003</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="J1:P1"/>
+    <mergeCell ref="R1:X1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B63F184-E8FA-644F-AABA-9AE0DF67F39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC772D-1C5C-3B41-84CA-BC50774A3058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="156">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -512,6 +512,122 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>TCI (LSTM-Tatt) nc=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) nc=3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) nc=5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) nc=7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) nc=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) d=64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) d=32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) d=128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) d=256</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lamb=0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几乎是硬约束（完全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>OT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) rho=0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI (LSTM-Tatt) tai=0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -520,7 +636,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -555,8 +671,15 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,6 +713,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -690,7 +819,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -713,6 +841,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -740,10 +872,24 @@
     <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1024,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1038,34 +1184,34 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20"/>
-      <c r="J1" s="21" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23"/>
+      <c r="J1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="23"/>
-      <c r="R1" s="24" t="s">
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="26"/>
+      <c r="R1" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="26"/>
-      <c r="Z1" s="17" t="s">
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="29"/>
+      <c r="Z1" s="16" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1141,73 +1287,73 @@
       </c>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0.56040000000000001</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>0.23549999999999999</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>0.39889999999999998</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>0.56769999999999998</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>0.61129999999999995</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>0.61719999999999997</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>0.62470000000000003</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0.51439999999999997</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <v>0.16520000000000001</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <v>0.32700000000000001</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <v>0.52700000000000002</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <v>0.54249999999999998</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="11">
         <v>0.55579999999999996</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="11">
         <v>0.57179999999999997</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="11">
         <v>0.50580000000000003</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="11">
         <v>0.19220000000000001</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="11">
         <v>0.36020000000000002</v>
       </c>
-      <c r="U3" s="12">
+      <c r="U3" s="11">
         <v>0.57509999999999994</v>
       </c>
-      <c r="V3" s="12">
+      <c r="V3" s="11">
         <v>0.73980000000000001</v>
       </c>
-      <c r="W3" s="12">
+      <c r="W3" s="11">
         <v>0.75119999999999998</v>
       </c>
-      <c r="X3" s="12">
+      <c r="X3" s="11">
         <v>0.75780000000000003</v>
       </c>
       <c r="Z3" s="2" t="s">
@@ -1215,68 +1361,68 @@
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="10"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="W4" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="12" t="s">
         <v>99</v>
       </c>
       <c r="Z4" s="2" t="s">
@@ -1284,70 +1430,70 @@
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>0.59360000000000002</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>0.24410000000000001</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>0.40649999999999997</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>0.63119999999999998</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>0.63549999999999995</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>0.62980000000000003</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>0.63160000000000005</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>0.56710000000000005</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>0.218</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>0.4</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>0.58199999999999996</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>0.67769999999999997</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>0.65869999999999995</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="10">
         <v>0.65449999999999997</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="10">
         <v>0.59740000000000004</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="10">
         <v>0.2394</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="10">
         <v>0.42920000000000003</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="10">
         <v>0.64639999999999997</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="10">
         <v>0.75509999999999999</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="10">
         <v>0.76939999999999997</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="10">
         <v>0.77639999999999998</v>
       </c>
       <c r="Z5" s="2" t="s">
@@ -1355,68 +1501,68 @@
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="10"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="13" t="s">
+      <c r="R6" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="T6" s="13" t="s">
+      <c r="T6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="U6" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="V6" s="13" t="s">
+      <c r="V6" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="W6" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="X6" s="13" t="s">
+      <c r="X6" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Z6" s="2" t="s">
@@ -1498,67 +1644,67 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="14" t="s">
+      <c r="S8" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="U8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="V8" s="14" t="s">
+      <c r="V8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="X8" s="14" t="s">
+      <c r="X8" s="13" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1634,67 +1780,67 @@
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="O10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="P10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="R10" s="14" t="s">
+      <c r="R10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="S10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="T10" s="14" t="s">
+      <c r="T10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="U10" s="14" t="s">
+      <c r="U10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="V10" s="14" t="s">
+      <c r="V10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="X10" s="14" t="s">
+      <c r="X10" s="13" t="s">
         <v>93</v>
       </c>
       <c r="Z10" s="2" t="s">
@@ -1702,70 +1848,70 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0.56340000000000001</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>0.20860000000000001</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>0.37740000000000001</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>0.5796</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>0.61270000000000002</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>0.61280000000000001</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>0.61919999999999997</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <v>0.54749999999999999</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <v>0.191</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <v>0.34720000000000001</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="11">
         <v>0.56179999999999997</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
         <v>0.49830000000000002</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="11">
         <v>0.53029999999999999</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="11">
         <v>0.55640000000000001</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="11">
         <v>0.57920000000000005</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="11">
         <v>0.20280000000000001</v>
       </c>
-      <c r="T11" s="12">
+      <c r="T11" s="11">
         <v>0.39410000000000001</v>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="11">
         <v>0.61980000000000002</v>
       </c>
-      <c r="V11" s="12">
+      <c r="V11" s="11">
         <v>0.73050000000000004</v>
       </c>
-      <c r="W11" s="12">
+      <c r="W11" s="11">
         <v>0.75160000000000005</v>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="11">
         <v>0.7631</v>
       </c>
       <c r="Z11" s="2" t="s">
@@ -1773,228 +1919,228 @@
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="10"/>
-      <c r="B12" s="13" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="O12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="R12" s="13" t="s">
+      <c r="R12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="T12" s="13" t="s">
+      <c r="T12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="U12" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="V12" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="W12" s="13" t="s">
+      <c r="W12" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="X12" s="13" t="s">
+      <c r="X12" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>0.60680000000000001</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>0.25480000000000003</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>0.44409999999999999</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>0.63439999999999996</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>0.66080000000000005</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <v>0.65629999999999999</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <v>0.65659999999999996</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <v>0.55320000000000003</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <v>0.2011</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <v>0.3528</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <v>0.57079999999999997</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="10">
         <v>0.53779999999999994</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="10">
         <v>0.55979999999999996</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="10">
         <v>0.57889999999999997</v>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="10">
         <v>0.59189999999999998</v>
       </c>
-      <c r="S13" s="11">
+      <c r="S13" s="10">
         <v>0.22550000000000001</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="10">
         <v>0.4249</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13" s="10">
         <v>0.63649999999999995</v>
       </c>
-      <c r="V13" s="11">
+      <c r="V13" s="10">
         <v>0.74860000000000004</v>
       </c>
-      <c r="W13" s="11">
+      <c r="W13" s="10">
         <v>0.76529999999999998</v>
       </c>
-      <c r="X13" s="11">
+      <c r="X13" s="10">
         <v>0.77310000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="10"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="M14" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="N14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="P14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="R14" s="13" t="s">
+      <c r="R14" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="S14" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="T14" s="13" t="s">
+      <c r="T14" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="U14" s="13" t="s">
+      <c r="U14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="V14" s="13" t="s">
+      <c r="V14" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="W14" s="13" t="s">
+      <c r="W14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="X14" s="13" t="s">
+      <c r="X14" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="31">
         <v>0.60840000000000005</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="31">
         <v>0.2387</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="31">
         <v>0.43230000000000002</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="31">
         <v>0.62580000000000002</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="31">
         <v>0.63500000000000001</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="31">
         <v>0.63470000000000004</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="31">
         <v>0.63729999999999998</v>
       </c>
       <c r="J15" s="5">
@@ -2041,93 +2187,94 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N16" s="14" t="s">
+      <c r="N16" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="14" t="s">
+      <c r="O16" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="P16" s="14" t="s">
+      <c r="P16" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="R16" s="14" t="s">
+      <c r="R16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="T16" s="14" t="s">
+      <c r="T16" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="U16" s="14" t="s">
+      <c r="U16" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="V16" s="14" t="s">
+      <c r="V16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="W16" s="14" t="s">
+      <c r="W16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="X16" s="14" t="s">
+      <c r="X16" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="33">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="33">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="33">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="33">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="33">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="33">
         <v>0.6492</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="33">
         <v>0.65200000000000002</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2180,278 +2327,278 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="15" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="15" t="s">
+      <c r="M18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="15" t="s">
+      <c r="N18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O18" s="15" t="s">
+      <c r="O18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="P18" s="15" t="s">
+      <c r="P18" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="R18" s="15" t="s">
+      <c r="R18" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="S18" s="15" t="s">
+      <c r="S18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="T18" s="15" t="s">
+      <c r="T18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="U18" s="15" t="s">
+      <c r="U18" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="V18" s="15" t="s">
+      <c r="V18" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W18" s="15" t="s">
+      <c r="W18" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="X18" s="15" t="s">
+      <c r="X18" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>0.59860000000000002</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>0.21940000000000001</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>0.40649999999999997</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="11">
         <v>0.63549999999999995</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <v>0.59489999999999998</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="11">
         <v>0.60780000000000001</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <v>0.6169</v>
       </c>
       <c r="I19" s="1"/>
-      <c r="J19" s="12">
+      <c r="J19" s="11">
         <v>0.55469999999999997</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <v>0.18540000000000001</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="11">
         <v>0.37869999999999998</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="10">
         <v>0.57750000000000001</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="11">
         <v>0.45440000000000003</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="11">
         <v>0.51600000000000001</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="11">
         <v>0.54549999999999998</v>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="11">
         <v>0.59089999999999998</v>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="11">
         <v>0.21590000000000001</v>
       </c>
-      <c r="T19" s="12">
+      <c r="T19" s="11">
         <v>0.41489999999999999</v>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="11">
         <v>0.64349999999999996</v>
       </c>
-      <c r="V19" s="12">
+      <c r="V19" s="11">
         <v>0.73219999999999996</v>
       </c>
-      <c r="W19" s="12">
+      <c r="W19" s="11">
         <v>0.74980000000000002</v>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="11">
         <v>0.76219999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="15" t="s">
         <v>58</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M20" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="N20" s="16" t="s">
+      <c r="N20" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="O20" s="16" t="s">
+      <c r="O20" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="P20" s="16" t="s">
+      <c r="P20" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="16" t="s">
+      <c r="R20" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="S20" s="16" t="s">
+      <c r="S20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="T20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="U20" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="V20" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="W20" s="16" t="s">
+      <c r="W20" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="X20" s="16" t="s">
+      <c r="X20" s="15" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:25" s="3" customFormat="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>0.60340000000000005</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>0.24299999999999999</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>0.41610000000000003</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <v>0.61009999999999998</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="10">
         <v>0.61809999999999998</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="10">
         <v>0.62529999999999997</v>
       </c>
       <c r="I21" s="1"/>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <v>0.56489999999999996</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <v>0.2034</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="10">
         <v>0.3831</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="11">
         <v>0.56969999999999998</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="10">
         <v>0.60350000000000004</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="10">
         <v>0.61040000000000005</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="10">
         <v>0.61260000000000003</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="10">
         <v>0.59499999999999997</v>
       </c>
-      <c r="S21" s="11">
+      <c r="S21" s="10">
         <v>0.2225</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="10">
         <v>0.43</v>
       </c>
-      <c r="U21" s="11">
+      <c r="U21" s="10">
         <v>0.6542</v>
       </c>
-      <c r="V21" s="11">
+      <c r="V21" s="10">
         <v>0.74509999999999998</v>
       </c>
-      <c r="W21" s="11">
+      <c r="W21" s="10">
         <v>0.76119999999999999</v>
       </c>
-      <c r="X21" s="11">
+      <c r="X21" s="10">
         <v>0.77290000000000003</v>
       </c>
       <c r="Y21" s="3" t="s">
@@ -2459,69 +2606,69 @@
       </c>
     </row>
     <row r="22" spans="1:25" s="3" customFormat="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="15" t="s">
         <v>85</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="L22" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M22" s="13" t="s">
+      <c r="M22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N22" s="13" t="s">
+      <c r="N22" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="O22" s="13" t="s">
+      <c r="O22" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="P22" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="16" t="s">
+      <c r="R22" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="13" t="s">
+      <c r="S22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="T22" s="13" t="s">
+      <c r="T22" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="U22" s="13" t="s">
+      <c r="U22" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="V22" s="13" t="s">
+      <c r="V22" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="W22" s="13" t="s">
+      <c r="W22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="X22" s="13" t="s">
+      <c r="X22" s="12" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2585,35 +2732,35 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
     </row>
     <row r="26" spans="1:25" s="3" customFormat="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>0.57450000000000001</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>0.24410000000000001</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <v>0.38529999999999998</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="11">
         <v>0.5706</v>
       </c>
       <c r="F26" s="4"/>
@@ -2636,29 +2783,29 @@
       <c r="X26" s="1"/>
     </row>
     <row r="27" spans="1:25" s="3" customFormat="1">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="12" t="s">
         <v>74</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="9"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="8"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2671,19 +2818,19 @@
       <c r="X27" s="4"/>
     </row>
     <row r="28" spans="1:25" s="3" customFormat="1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>0.59050000000000002</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <v>0.23530000000000001</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>0.4118</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <v>0.60289999999999999</v>
       </c>
       <c r="F28" s="4"/>
@@ -2706,19 +2853,19 @@
       <c r="X28" s="4"/>
     </row>
     <row r="29" spans="1:25" s="3" customFormat="1">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="4"/>
@@ -2776,19 +2923,19 @@
       <c r="X30" s="4"/>
     </row>
     <row r="31" spans="1:25" s="3" customFormat="1">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>33</v>
       </c>
       <c r="F31" s="4"/>
@@ -2846,19 +2993,19 @@
       <c r="X32" s="1"/>
     </row>
     <row r="33" spans="1:24" s="3" customFormat="1">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="4"/>
@@ -2881,19 +3028,19 @@
       <c r="X33" s="1"/>
     </row>
     <row r="34" spans="1:24" s="3" customFormat="1">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="31">
         <v>0.60840000000000005</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="31">
         <v>0.2387</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="31">
         <v>0.43230000000000002</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="31">
         <v>0.62580000000000002</v>
       </c>
       <c r="F34" s="4"/>
@@ -2916,19 +3063,19 @@
       <c r="X34" s="1"/>
     </row>
     <row r="35" spans="1:24" s="3" customFormat="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="32" t="s">
         <v>120</v>
       </c>
       <c r="F35" s="4"/>
@@ -2951,19 +3098,19 @@
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="1:24">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="33">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="33">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="33">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="33">
         <v>0.64729999999999999</v>
       </c>
       <c r="F36" s="4"/>
@@ -2971,19 +3118,19 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="35" t="s">
         <v>121</v>
       </c>
       <c r="F37" s="4"/>
@@ -3011,19 +3158,19 @@
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="F39" s="4"/>
@@ -3051,19 +3198,19 @@
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:24">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="13" t="s">
         <v>43</v>
       </c>
       <c r="F41" s="4"/>
@@ -3071,19 +3218,19 @@
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <v>0.58909999999999996</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>0.21490000000000001</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="11">
         <v>0.4032</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="11">
         <v>0.60719999999999996</v>
       </c>
       <c r="F42" s="4"/>
@@ -3091,19 +3238,19 @@
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:24">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="4"/>
@@ -3111,19 +3258,19 @@
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:24">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>0.59489999999999998</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="11">
         <v>0.21160000000000001</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <v>0.41039999999999999</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="10">
         <v>0.63370000000000004</v>
       </c>
       <c r="F44" s="4"/>
@@ -3131,19 +3278,19 @@
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:24">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F45" s="4"/>
@@ -3171,19 +3318,19 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="4"/>
@@ -3210,40 +3357,40 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="27" t="s">
+    <row r="49" spans="1:9">
+      <c r="A49" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="13" t="s">
         <v>24</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="10" t="s">
+    <row r="50" spans="1:9">
+      <c r="A50" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="11">
         <v>0.59140000000000004</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>0.21759999999999999</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <v>0.39610000000000001</v>
       </c>
-      <c r="E50" s="12">
+      <c r="E50" s="11">
         <v>0.61599999999999999</v>
       </c>
       <c r="F50" s="4" t="s">
@@ -3252,75 +3399,607 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="29" t="s">
+    <row r="51" spans="1:9">
+      <c r="A51" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="12" t="s">
         <v>95</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="10" t="s">
+    <row r="52" spans="1:9">
+      <c r="A52" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>0.58919999999999995</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="11">
         <v>0.2041</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="11">
         <v>0.39169999999999999</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="10">
         <v>0.62880000000000003</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="29" t="s">
+    <row r="53" spans="1:9">
+      <c r="A53" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9">
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9">
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="5">
+        <v>0.61270000000000002</v>
+      </c>
+      <c r="C56" s="5">
+        <v>0.26479999999999998</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0.45619999999999999</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0.64649999999999996</v>
+      </c>
+      <c r="F56" s="5">
+        <v>0.63890000000000002</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0.64070000000000005</v>
+      </c>
+      <c r="H56" s="5">
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" s="31">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C57" s="31">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D57" s="31">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E57" s="31">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F57" s="31">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G57" s="31">
+        <v>0.6492</v>
+      </c>
+      <c r="H57" s="31">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="5">
+        <v>0.6099</v>
+      </c>
+      <c r="C58" s="5">
+        <v>0.2495</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0.44090000000000001</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F58" s="5">
+        <v>0.64070000000000005</v>
+      </c>
+      <c r="G58" s="5">
+        <v>0.64610000000000001</v>
+      </c>
+      <c r="H58" s="5">
+        <v>0.64839999999999998</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="5">
+        <v>0.61339999999999995</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0.2581</v>
+      </c>
+      <c r="D59" s="5">
+        <v>0.43959999999999999</v>
+      </c>
+      <c r="E59" s="5">
+        <v>0.65810000000000002</v>
+      </c>
+      <c r="F59" s="5">
+        <v>0.63619999999999999</v>
+      </c>
+      <c r="G59" s="5">
+        <v>0.63880000000000003</v>
+      </c>
+      <c r="H59" s="5">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="5">
+        <v>0.6119</v>
+      </c>
+      <c r="C61" s="5">
+        <v>0.2409</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0.44190000000000002</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0.63980000000000004</v>
+      </c>
+      <c r="F61" s="5">
+        <v>0.64159999999999995</v>
+      </c>
+      <c r="G61" s="5">
+        <v>0.64590000000000003</v>
+      </c>
+      <c r="H61" s="5">
+        <v>0.64239999999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="31">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C62" s="31">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D62" s="31">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E62" s="31">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F62" s="31">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G62" s="31">
+        <v>0.6492</v>
+      </c>
+      <c r="H62" s="31">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="5">
+        <v>0.61829999999999996</v>
+      </c>
+      <c r="C63" s="5">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="D63" s="5">
+        <v>0.45269999999999999</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="F63" s="5">
+        <v>0.64159999999999995</v>
+      </c>
+      <c r="G63" s="5">
+        <v>0.66190000000000004</v>
+      </c>
+      <c r="H63" s="5">
+        <v>0.65010000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="5">
+        <v>0.60140000000000005</v>
+      </c>
+      <c r="C64" s="5">
+        <v>0.26229999999999998</v>
+      </c>
+      <c r="D64" s="5">
+        <v>0.45229999999999998</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0.63980000000000004</v>
+      </c>
+      <c r="F64" s="5">
+        <v>0.63949999999999996</v>
+      </c>
+      <c r="G64" s="5">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="H64" s="5">
+        <v>0.65329999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="5">
+        <v>0.60060000000000002</v>
+      </c>
+      <c r="C65" s="5">
+        <v>0.25159999999999999</v>
+      </c>
+      <c r="D65" s="5">
+        <v>0.44519999999999998</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.63580000000000003</v>
+      </c>
+      <c r="F65" s="5">
+        <v>0.63770000000000004</v>
+      </c>
+      <c r="G65" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="H65" s="5">
+        <v>0.64980000000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="5">
+        <v>0.5877</v>
+      </c>
+      <c r="C67" s="5">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="E67" s="5">
+        <v>0.60540000000000005</v>
+      </c>
+      <c r="F67" s="5">
+        <v>0.57179999999999997</v>
+      </c>
+      <c r="G67" s="5">
+        <v>0.59030000000000005</v>
+      </c>
+      <c r="H67" s="5">
+        <v>0.60409999999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="5">
+        <v>0.61519999999999997</v>
+      </c>
+      <c r="C68" s="5">
+        <v>0.27529999999999999</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0.46239999999999998</v>
+      </c>
+      <c r="E68" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F68" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="G68" s="5">
+        <v>0.64339999999999997</v>
+      </c>
+      <c r="H68" s="5">
+        <v>0.64639999999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="31">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C69" s="31">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D69" s="31">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E69" s="31">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F69" s="31">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G69" s="31">
+        <v>0.6492</v>
+      </c>
+      <c r="H69" s="31">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="5">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="C70" s="5">
+        <v>0.27850000000000003</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0.45379999999999998</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0.64270000000000005</v>
+      </c>
+      <c r="F70" s="5">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="G70" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="H70" s="5">
+        <v>0.64910000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="5">
+        <v>0.62519999999999998</v>
+      </c>
+      <c r="C71" s="5">
+        <v>0.27110000000000001</v>
+      </c>
+      <c r="D71" s="5">
+        <v>0.45119999999999999</v>
+      </c>
+      <c r="E71" s="5">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="F71" s="5">
+        <v>0.64290000000000003</v>
+      </c>
+      <c r="G71" s="5">
+        <v>0.64449999999999996</v>
+      </c>
+      <c r="H71" s="5">
+        <v>0.6502</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="5">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="C72" s="5">
+        <v>0.24729999999999999</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0.44729999999999998</v>
+      </c>
+      <c r="E72" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F72" s="5">
+        <v>0.59709999999999996</v>
+      </c>
+      <c r="G72" s="5">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="H72" s="5">
+        <v>0.62350000000000005</v>
+      </c>
+      <c r="I72" s="39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="5">
+        <v>0.61519999999999997</v>
+      </c>
+      <c r="C74" s="5">
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0.4516</v>
+      </c>
+      <c r="E74" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F74" s="5">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="G74" s="5">
+        <v>0.64539999999999997</v>
+      </c>
+      <c r="H74" s="5">
+        <v>0.65049999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="31">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C75" s="31">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D75" s="31">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E75" s="31">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F75" s="31">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G75" s="31">
+        <v>0.6492</v>
+      </c>
+      <c r="H75" s="31">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="5">
+        <v>0.61080000000000001</v>
+      </c>
+      <c r="C76" s="5">
+        <v>0.2676</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.4466</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F76" s="5">
+        <v>0.64680000000000004</v>
+      </c>
+      <c r="G76" s="5">
+        <v>0.64810000000000001</v>
+      </c>
+      <c r="H76" s="5">
+        <v>0.65069999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="5">
+        <v>0.61029999999999995</v>
+      </c>
+      <c r="C77" s="5">
+        <v>0.25590000000000002</v>
+      </c>
+      <c r="D77" s="5">
+        <v>0.43759999999999999</v>
+      </c>
+      <c r="E77" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F77" s="5">
+        <v>0.64090000000000003</v>
+      </c>
+      <c r="G77" s="5">
+        <v>0.64370000000000005</v>
+      </c>
+      <c r="H77" s="5">
+        <v>0.64970000000000006</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="5">
+        <v>0.61360000000000003</v>
+      </c>
+      <c r="C78" s="5">
+        <v>0.2591</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="E78" s="5">
+        <v>0.65590000000000004</v>
+      </c>
+      <c r="F78" s="5">
+        <v>0.64090000000000003</v>
+      </c>
+      <c r="G78" s="5">
+        <v>0.64149999999999996</v>
+      </c>
+      <c r="H78" s="5">
+        <v>0.64249999999999996</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC772D-1C5C-3B41-84CA-BC50774A3058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48D9B47-1F33-6343-8ACA-68055B0B3B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="168">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -626,6 +626,82 @@
   </si>
   <si>
     <t>TCI (LSTM-Tatt) tai=0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ablation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI - InvLoss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI - OtLoss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.027)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.033)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.041)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI - Lamb Decay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.030)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.028)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这里就是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>slightly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>降低效果</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI - WeightProb in Eval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.031)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -807,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -845,6 +921,23 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -872,24 +965,6 @@
     <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1170,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1184,33 +1259,33 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="23"/>
-      <c r="J1" s="24" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32"/>
+      <c r="J1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="26"/>
-      <c r="R1" s="27" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="35"/>
+      <c r="R1" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="29"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="38"/>
       <c r="Z1" s="16" t="s">
         <v>49</v>
       </c>
@@ -2119,29 +2194,29 @@
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="31">
-        <v>0.60840000000000005</v>
-      </c>
-      <c r="C15" s="31">
-        <v>0.2387</v>
-      </c>
-      <c r="D15" s="31">
-        <v>0.43230000000000002</v>
-      </c>
-      <c r="E15" s="31">
-        <v>0.62580000000000002</v>
-      </c>
-      <c r="F15" s="31">
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="G15" s="31">
-        <v>0.63470000000000004</v>
-      </c>
-      <c r="H15" s="31">
-        <v>0.63729999999999998</v>
+      <c r="B15" s="22">
+        <v>0.59840000000000004</v>
+      </c>
+      <c r="C15" s="22">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0.42230000000000001</v>
+      </c>
+      <c r="E15" s="22">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="F15" s="22">
+        <v>0.625</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0.62470000000000003</v>
+      </c>
+      <c r="H15" s="22">
+        <v>0.62729999999999997</v>
       </c>
       <c r="J15" s="5">
         <v>0.5393</v>
@@ -2187,26 +2262,26 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="30"/>
-      <c r="B16" s="32" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="23" t="s">
         <v>125</v>
       </c>
       <c r="J16" s="13" t="s">
@@ -2253,28 +2328,28 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="24">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="24">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="24">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="24">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="24">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="24">
         <v>0.6492</v>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="24">
         <v>0.65200000000000002</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2327,26 +2402,26 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="26" t="s">
         <v>122</v>
       </c>
       <c r="J18" s="14" t="s">
@@ -2697,390 +2772,269 @@
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
     </row>
-    <row r="24" spans="1:25" s="3" customFormat="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" s="3" customFormat="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-    </row>
-    <row r="26" spans="1:25" s="3" customFormat="1">
-      <c r="A26" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="11">
-        <v>0.57450000000000001</v>
-      </c>
-      <c r="C26" s="10">
-        <v>0.24410000000000001</v>
-      </c>
-      <c r="D26" s="11">
-        <v>0.38529999999999998</v>
-      </c>
-      <c r="E26" s="11">
-        <v>0.5706</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" s="3" customFormat="1">
-      <c r="A27" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-    </row>
-    <row r="28" spans="1:25" s="3" customFormat="1">
-      <c r="A28" s="9" t="s">
+    <row r="24" spans="1:25">
+      <c r="A24" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="10">
-        <v>0.59050000000000002</v>
-      </c>
-      <c r="C28" s="11">
-        <v>0.23530000000000001</v>
-      </c>
-      <c r="D28" s="10">
-        <v>0.4118</v>
-      </c>
-      <c r="E28" s="10">
-        <v>0.60289999999999999</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-    </row>
-    <row r="29" spans="1:25" s="3" customFormat="1">
-      <c r="A29" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="12" t="s">
+      <c r="B25" s="24">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C25" s="24">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D25" s="24">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E25" s="24">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F25" s="24">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G25" s="24">
+        <v>0.6492</v>
+      </c>
+      <c r="H25" s="24">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-    </row>
-    <row r="30" spans="1:25" s="3" customFormat="1">
-      <c r="A30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.59040000000000004</v>
-      </c>
-      <c r="C30" s="5">
-        <v>0.22189999999999999</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0.41880000000000001</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0.61560000000000004</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-    </row>
-    <row r="31" spans="1:25" s="3" customFormat="1">
-      <c r="A31" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="14" t="s">
+      <c r="D26" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.60570000000000002</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.21940000000000001</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0.40749999999999997</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.66769999999999996</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.61890000000000001</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.62109999999999999</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0.62849999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="B28" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.59660000000000002</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.2344</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.6129</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.59509999999999996</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0.60799999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="B30" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="5">
+        <v>0.60609999999999997</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0.43009999999999998</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0.62949999999999995</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0.63319999999999999</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0.63629999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="B32" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
+      <c r="A33" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.61350000000000005</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.26769999999999999</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0.43440000000000001</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.63970000000000005</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0.64839999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24">
+      <c r="B34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-    </row>
-    <row r="32" spans="1:25" s="3" customFormat="1">
-      <c r="A32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="6">
-        <v>0.60450000000000004</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.24840000000000001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.61880000000000002</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-    </row>
-    <row r="33" spans="1:24" s="3" customFormat="1">
-      <c r="A33" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-    </row>
-    <row r="34" spans="1:24" s="3" customFormat="1">
-      <c r="A34" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="31">
-        <v>0.60840000000000005</v>
-      </c>
-      <c r="C34" s="31">
-        <v>0.2387</v>
-      </c>
-      <c r="D34" s="31">
-        <v>0.43230000000000002</v>
-      </c>
-      <c r="E34" s="31">
-        <v>0.62580000000000002</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
+      <c r="E34" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="35" spans="1:24" s="3" customFormat="1">
-      <c r="A35" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -3097,907 +3051,1282 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
     </row>
-    <row r="36" spans="1:24">
-      <c r="A36" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="33">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C36" s="33">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D36" s="33">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E36" s="33">
-        <v>0.64729999999999999</v>
-      </c>
+    <row r="36" spans="1:24" s="3" customFormat="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:24">
-      <c r="A37" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>121</v>
+      <c r="I36" s="1"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+    </row>
+    <row r="37" spans="1:24" s="3" customFormat="1">
+      <c r="A37" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="11">
+        <v>0.57450000000000001</v>
+      </c>
+      <c r="C37" s="10">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="D37" s="11">
+        <v>0.38529999999999998</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0.5706</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:24">
-      <c r="A38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="5">
-        <v>0.59119999999999995</v>
-      </c>
-      <c r="C38" s="5">
-        <v>0.2082</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0.40820000000000001</v>
-      </c>
-      <c r="E38" s="5">
-        <v>0.60329999999999995</v>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+    </row>
+    <row r="38" spans="1:24" s="3" customFormat="1">
+      <c r="A38" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:24">
-      <c r="A39" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>33</v>
+      <c r="I38" s="1"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+    </row>
+    <row r="39" spans="1:24" s="3" customFormat="1">
+      <c r="A39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="10">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="C39" s="11">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="D39" s="10">
+        <v>0.4118</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.60289999999999999</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:24">
-      <c r="A40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="6">
-        <v>0.60209999999999997</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.2283</v>
-      </c>
-      <c r="D40" s="6">
-        <v>0.41089999999999999</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.63100000000000001</v>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+    </row>
+    <row r="40" spans="1:24" s="3" customFormat="1">
+      <c r="A40" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:24">
-      <c r="A41" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>43</v>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+    </row>
+    <row r="41" spans="1:24" s="3" customFormat="1">
+      <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="5">
+        <v>0.59040000000000004</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.41880000000000001</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.61560000000000004</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:24">
-      <c r="A42" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="11">
-        <v>0.58909999999999996</v>
-      </c>
-      <c r="C42" s="10">
-        <v>0.21490000000000001</v>
-      </c>
-      <c r="D42" s="11">
-        <v>0.4032</v>
-      </c>
-      <c r="E42" s="11">
-        <v>0.60719999999999996</v>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+    </row>
+    <row r="42" spans="1:24" s="3" customFormat="1">
+      <c r="A42" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:24">
-      <c r="A43" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>26</v>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+    </row>
+    <row r="43" spans="1:24" s="3" customFormat="1">
+      <c r="A43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0.60450000000000004</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.24840000000000001</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.61880000000000002</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:24">
-      <c r="A44" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="10">
-        <v>0.59489999999999998</v>
-      </c>
-      <c r="C44" s="11">
-        <v>0.21160000000000001</v>
-      </c>
-      <c r="D44" s="10">
-        <v>0.41039999999999999</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.63370000000000004</v>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+    </row>
+    <row r="44" spans="1:24" s="3" customFormat="1">
+      <c r="A44" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:24">
-      <c r="A45" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>24</v>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+    </row>
+    <row r="45" spans="1:24" s="3" customFormat="1">
+      <c r="A45" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="22">
+        <v>0.59840000000000004</v>
+      </c>
+      <c r="C45" s="22">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="D45" s="22">
+        <v>0.42230000000000001</v>
+      </c>
+      <c r="E45" s="22">
+        <v>0.61580000000000001</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:24">
-      <c r="A46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="5">
-        <v>0.59130000000000005</v>
-      </c>
-      <c r="C46" s="6">
-        <v>0.21640000000000001</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0.40150000000000002</v>
-      </c>
-      <c r="E46" s="5">
-        <v>0.6179</v>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+    </row>
+    <row r="46" spans="1:24" s="3" customFormat="1">
+      <c r="A46" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>120</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>17</v>
+      <c r="A47" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="24">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C47" s="24">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D47" s="24">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E47" s="24">
+        <v>0.64729999999999999</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:24">
-      <c r="A48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="6">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="C48" s="5">
-        <v>0.2094</v>
-      </c>
-      <c r="D48" s="6">
-        <v>0.41089999999999999</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.63580000000000003</v>
+      <c r="A48" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>24</v>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="5">
+        <v>0.59119999999999995</v>
+      </c>
+      <c r="C49" s="5">
+        <v>0.2082</v>
+      </c>
+      <c r="D49" s="5">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0.60329999999999995</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="11">
-        <v>0.59140000000000004</v>
-      </c>
-      <c r="C50" s="10">
-        <v>0.21759999999999999</v>
-      </c>
-      <c r="D50" s="10">
-        <v>0.39610000000000001</v>
-      </c>
-      <c r="E50" s="11">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>133</v>
-      </c>
+    <row r="50" spans="1:8">
+      <c r="A50" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>95</v>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0.60209999999999997</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.2283</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.63100000000000001</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="10">
-        <v>0.58919999999999995</v>
-      </c>
-      <c r="C52" s="11">
-        <v>0.2041</v>
-      </c>
-      <c r="D52" s="11">
-        <v>0.39169999999999999</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0.62880000000000003</v>
+    <row r="52" spans="1:8">
+      <c r="A52" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>17</v>
+    <row r="53" spans="1:8">
+      <c r="A53" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="11">
+        <v>0.58909999999999996</v>
+      </c>
+      <c r="C53" s="10">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0.4032</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0.60719999999999996</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:8">
+      <c r="A54" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:8">
+      <c r="A55" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="10">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="C55" s="11">
+        <v>0.21160000000000001</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.63370000000000004</v>
+      </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="38" t="s">
+    <row r="56" spans="1:8">
+      <c r="A56" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="5">
+        <v>0.59130000000000005</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="D57" s="5">
+        <v>0.40150000000000002</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.6179</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="6">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0.2094</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.63580000000000003</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="11">
+        <v>0.59140000000000004</v>
+      </c>
+      <c r="C61" s="10">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="D61" s="10">
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="E61" s="11">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="10">
+        <v>0.58919999999999995</v>
+      </c>
+      <c r="C63" s="11">
+        <v>0.2041</v>
+      </c>
+      <c r="D63" s="11">
+        <v>0.39169999999999999</v>
+      </c>
+      <c r="E63" s="10">
+        <v>0.62880000000000003</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B67" s="5">
         <v>0.61270000000000002</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C67" s="5">
         <v>0.26479999999999998</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D67" s="5">
         <v>0.45619999999999999</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E67" s="5">
         <v>0.64649999999999996</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F67" s="5">
         <v>0.63890000000000002</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G67" s="5">
         <v>0.64070000000000005</v>
       </c>
-      <c r="H56" s="5">
+      <c r="H67" s="5">
         <v>0.64470000000000005</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="30" t="s">
+    <row r="68" spans="1:9">
+      <c r="A68" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B57" s="31">
+      <c r="B68" s="22">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C68" s="22">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D68" s="22">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E68" s="22">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F68" s="22">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G68" s="22">
         <v>0.6492</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H68" s="22">
         <v>0.65200000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="38" t="s">
+    <row r="69" spans="1:9">
+      <c r="A69" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B69" s="5">
         <v>0.6099</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C69" s="5">
         <v>0.2495</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D69" s="5">
         <v>0.44090000000000001</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E69" s="5">
         <v>0.63439999999999996</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F69" s="5">
         <v>0.64070000000000005</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G69" s="5">
         <v>0.64610000000000001</v>
       </c>
-      <c r="H58" s="5">
+      <c r="H69" s="5">
         <v>0.64839999999999998</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="38" t="s">
+    <row r="70" spans="1:9">
+      <c r="A70" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B70" s="5">
         <v>0.61339999999999995</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C70" s="5">
         <v>0.2581</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D70" s="5">
         <v>0.43959999999999999</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E70" s="5">
         <v>0.65810000000000002</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F70" s="5">
         <v>0.63619999999999999</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G70" s="5">
         <v>0.63880000000000003</v>
       </c>
-      <c r="H59" s="5">
+      <c r="H70" s="5">
         <v>0.64500000000000002</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="38" t="s">
+    <row r="72" spans="1:9">
+      <c r="A72" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B72" s="5">
         <v>0.6119</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C72" s="5">
         <v>0.2409</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D72" s="5">
         <v>0.44190000000000002</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E72" s="5">
         <v>0.63980000000000004</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F72" s="5">
         <v>0.64159999999999995</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G72" s="5">
         <v>0.64590000000000003</v>
       </c>
-      <c r="H61" s="5">
+      <c r="H72" s="5">
         <v>0.64239999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="30" t="s">
+    <row r="73" spans="1:9">
+      <c r="A73" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B73" s="22">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C73" s="22">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D73" s="22">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E73" s="22">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F73" s="22">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G73" s="22">
         <v>0.6492</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H73" s="22">
         <v>0.65200000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="38" t="s">
+    <row r="74" spans="1:9">
+      <c r="A74" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B74" s="5">
         <v>0.61829999999999996</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C74" s="5">
         <v>0.27100000000000002</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D74" s="5">
         <v>0.45269999999999999</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E74" s="5">
         <v>0.65700000000000003</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F74" s="5">
         <v>0.64159999999999995</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G74" s="5">
         <v>0.66190000000000004</v>
       </c>
-      <c r="H63" s="5">
+      <c r="H74" s="5">
         <v>0.65010000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="38" t="s">
+    <row r="75" spans="1:9">
+      <c r="A75" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B75" s="5">
         <v>0.60140000000000005</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C75" s="5">
         <v>0.26229999999999998</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D75" s="5">
         <v>0.45229999999999998</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E75" s="5">
         <v>0.63980000000000004</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F75" s="5">
         <v>0.63949999999999996</v>
       </c>
-      <c r="G64" s="5">
+      <c r="G75" s="5">
         <v>0.66300000000000003</v>
       </c>
-      <c r="H64" s="5">
+      <c r="H75" s="5">
         <v>0.65329999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="38" t="s">
+    <row r="76" spans="1:9">
+      <c r="A76" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B76" s="5">
         <v>0.60060000000000002</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C76" s="5">
         <v>0.25159999999999999</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D76" s="5">
         <v>0.44519999999999998</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E76" s="5">
         <v>0.63580000000000003</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F76" s="5">
         <v>0.63770000000000004</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G76" s="5">
         <v>0.63790000000000002</v>
       </c>
-      <c r="H65" s="5">
+      <c r="H76" s="5">
         <v>0.64980000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="38" t="s">
+    <row r="78" spans="1:9">
+      <c r="A78" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B78" s="5">
         <v>0.5877</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C78" s="5">
         <v>0.24299999999999999</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D78" s="5">
         <v>0.41399999999999998</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E78" s="5">
         <v>0.60540000000000005</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F78" s="5">
         <v>0.57179999999999997</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G78" s="5">
         <v>0.59030000000000005</v>
       </c>
-      <c r="H67" s="5">
+      <c r="H78" s="5">
         <v>0.60409999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="38" t="s">
+    <row r="79" spans="1:9">
+      <c r="A79" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B79" s="5">
         <v>0.61519999999999997</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C79" s="5">
         <v>0.27529999999999999</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D79" s="5">
         <v>0.46239999999999998</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E79" s="5">
         <v>0.63439999999999996</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F79" s="5">
         <v>0.63790000000000002</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G79" s="5">
         <v>0.64339999999999997</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H79" s="5">
         <v>0.64639999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="30" t="s">
+    <row r="80" spans="1:9">
+      <c r="A80" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="31">
+      <c r="B80" s="22">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C80" s="22">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D80" s="22">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E80" s="22">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F80" s="22">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G80" s="22">
         <v>0.6492</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H80" s="22">
         <v>0.65200000000000002</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="38" t="s">
+    <row r="81" spans="1:9">
+      <c r="A81" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B81" s="5">
         <v>0.61799999999999999</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C81" s="5">
         <v>0.27850000000000003</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D81" s="5">
         <v>0.45379999999999998</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E81" s="5">
         <v>0.64270000000000005</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F81" s="5">
         <v>0.64659999999999995</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G81" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H81" s="5">
         <v>0.64910000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="38" t="s">
+    <row r="82" spans="1:9">
+      <c r="A82" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B82" s="5">
         <v>0.62519999999999998</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C82" s="5">
         <v>0.27110000000000001</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D82" s="5">
         <v>0.45119999999999999</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E82" s="5">
         <v>0.64659999999999995</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F82" s="5">
         <v>0.64290000000000003</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G82" s="5">
         <v>0.64449999999999996</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H82" s="5">
         <v>0.6502</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="38" t="s">
+    <row r="83" spans="1:9">
+      <c r="A83" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B83" s="5">
         <v>0.60870000000000002</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C83" s="5">
         <v>0.24729999999999999</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D83" s="5">
         <v>0.44729999999999998</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E83" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F83" s="5">
         <v>0.59709999999999996</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G83" s="5">
         <v>0.61409999999999998</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H83" s="5">
         <v>0.62350000000000005</v>
       </c>
-      <c r="I72" s="39" t="s">
+      <c r="I83" s="29" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="38" t="s">
+    <row r="85" spans="1:9">
+      <c r="A85" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B85" s="5">
         <v>0.61519999999999997</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C85" s="5">
         <v>0.25380000000000003</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D85" s="5">
         <v>0.4516</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E85" s="5">
         <v>0.64549999999999996</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F85" s="5">
         <v>0.64600000000000002</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G85" s="5">
         <v>0.64539999999999997</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H85" s="5">
         <v>0.65049999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="30" t="s">
+    <row r="86" spans="1:9">
+      <c r="A86" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B75" s="31">
+      <c r="B86" s="22">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C86" s="22">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D75" s="31">
+      <c r="D86" s="22">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E86" s="22">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F75" s="31">
+      <c r="F86" s="22">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G75" s="31">
+      <c r="G86" s="22">
         <v>0.6492</v>
       </c>
-      <c r="H75" s="31">
+      <c r="H86" s="22">
         <v>0.65200000000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="38" t="s">
+    <row r="87" spans="1:9">
+      <c r="A87" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B87" s="5">
         <v>0.61080000000000001</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C87" s="5">
         <v>0.2676</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D87" s="5">
         <v>0.4466</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E87" s="5">
         <v>0.64549999999999996</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F87" s="5">
         <v>0.64680000000000004</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G87" s="5">
         <v>0.64810000000000001</v>
       </c>
-      <c r="H76" s="5">
+      <c r="H87" s="5">
         <v>0.65069999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="38" t="s">
+    <row r="88" spans="1:9">
+      <c r="A88" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B88" s="5">
         <v>0.61029999999999995</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C88" s="5">
         <v>0.25590000000000002</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D88" s="5">
         <v>0.43759999999999999</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E88" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F88" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G88" s="5">
         <v>0.64370000000000005</v>
       </c>
-      <c r="H77" s="5">
+      <c r="H88" s="5">
         <v>0.64970000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="38" t="s">
+    <row r="89" spans="1:9">
+      <c r="A89" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B89" s="5">
         <v>0.61360000000000003</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C89" s="5">
         <v>0.2591</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D89" s="5">
         <v>0.42370000000000002</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E89" s="5">
         <v>0.65590000000000004</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F89" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G89" s="5">
         <v>0.64149999999999996</v>
       </c>
-      <c r="H78" s="5">
+      <c r="H89" s="5">
         <v>0.64249999999999996</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48D9B47-1F33-6343-8ACA-68055B0B3B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B1633-E624-564B-9AF6-76ADB2E0E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="204">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -702,6 +702,233 @@
   </si>
   <si>
     <t>(0.031)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.024)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shazeer, N., Mirhoseini, A., Maziarz, K., Davis, A., Le, Q., Hinton, G., &amp; Dean, J. (2017). Outrageously large neural networks: The sparsely-gated mixture-of-experts layer.International Conference on Learning Representations.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统性地引入并推广了负载均衡辅助损失，防止路由塌缩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLOE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>把</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>线性模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当成一个原子单位，复制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>份作为专家，让它们各自独立地做完整预测，最后加权融合</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5725</t>
+  </si>
+  <si>
+    <t>0.2035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3971</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6261</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.014)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCdetector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双注意力+纯对比学习方法+噪声增强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动注入多种类型的异常作为负样本对比学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARLA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2313</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3986</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5568</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.032)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适用于零售的库存预测经典方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6067</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>MoE</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salinas, D., Flunkert, V., Gasthaus, J., &amp; Januschowski, T. (2020). DeepAR: Probabilistic forecasting with autoregressive recurrent networks. International journal of forecasting, 36(3), 1181-1191.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMOE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.034)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ni, R., Lin, Z., Wang, S., &amp; Fanti, G. (2024, April). Mixture-of-linear-experts for long-term time series forecasting. In International conference on artificial intelligence and statistics (pp. 4672-4680). PMLR.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yang, Y., Zhang, C., Zhou, T., Wen, Q., &amp; Sun, L. (2023, August). Dcdetector: Dual attention contrastive representation learning for time series anomaly detection. In Proceedings of the 29th ACM SIGKDD conference on knowledge discovery and data mining (pp. 3033-3045).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Darban, Z. Z., Webb, G. I., Pan, S., Aggarwal, C. C., &amp; Salehi, M. (2025). CARLA: Self-supervised contrastive representation learning for time series anomaly detection. Pattern Recognition, 157, 110874.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -883,7 +1110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -938,6 +1165,7 @@
     <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1245,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z89"/>
+  <dimension ref="A1:Z105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1259,33 +1487,33 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
+      <c r="J1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="35"/>
-      <c r="R1" s="36" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="36"/>
+      <c r="R1" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="39"/>
       <c r="Z1" s="16" t="s">
         <v>49</v>
       </c>
@@ -2772,1561 +3000,1974 @@
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
     </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="24" spans="1:25" s="3" customFormat="1">
+      <c r="A24" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="24">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C25" s="24">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D25" s="24">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E25" s="24">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F25" s="24">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G25" s="24">
-        <v>0.6492</v>
-      </c>
-      <c r="H25" s="24">
-        <v>0.65200000000000002</v>
+      <c r="A25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0.6048</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.23050000000000001</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.41560000000000002</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.62019999999999997</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.62909999999999999</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0.6391</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="26" t="s">
+      <c r="B26" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="D26" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>122</v>
+      <c r="G26" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I26" s="30" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B27" s="5">
-        <v>0.60570000000000002</v>
+        <v>0.55579999999999996</v>
       </c>
       <c r="C27" s="5">
-        <v>0.21940000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D27" s="5">
-        <v>0.40749999999999997</v>
+        <v>0.35909999999999997</v>
       </c>
       <c r="E27" s="5">
-        <v>0.66769999999999996</v>
+        <v>0.58169999999999999</v>
       </c>
       <c r="F27" s="5">
-        <v>0.61890000000000001</v>
+        <v>0.5827</v>
       </c>
       <c r="G27" s="5">
-        <v>0.62109999999999999</v>
+        <v>0.58789999999999998</v>
       </c>
       <c r="H27" s="5">
-        <v>0.62849999999999995</v>
+        <v>0.59960000000000002</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="B28" s="14" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>96</v>
+        <v>164</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="B29" s="5">
-        <v>0.59660000000000002</v>
+        <v>0.60519999999999996</v>
       </c>
       <c r="C29" s="5">
-        <v>0.2344</v>
+        <v>0.2455</v>
       </c>
       <c r="D29" s="5">
-        <v>0.42580000000000001</v>
+        <v>0.41610000000000003</v>
       </c>
       <c r="E29" s="5">
-        <v>0.6129</v>
+        <v>0.59530000000000005</v>
       </c>
       <c r="F29" s="5">
-        <v>0.57399999999999995</v>
+        <v>0.62980000000000003</v>
       </c>
       <c r="G29" s="5">
-        <v>0.59509999999999996</v>
+        <v>0.6331</v>
       </c>
       <c r="H29" s="5">
-        <v>0.60799999999999998</v>
+        <v>0.63470000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="B30" s="14" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>161</v>
+        <v>122</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="5">
-        <v>0.60609999999999997</v>
-      </c>
-      <c r="C31" s="5">
-        <v>0.25700000000000001</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.43009999999999998</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0.62949999999999995</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0.63319999999999999</v>
-      </c>
-      <c r="H31" s="5">
-        <v>0.63629999999999998</v>
+        <v>173</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="B32" s="14" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>164</v>
       </c>
       <c r="E32" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H32" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="I32" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.56430000000000002</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.2205</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0.40749999999999997</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0.59730000000000005</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0.60040000000000004</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="B34" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="I34" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="B36" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="F36" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I36" s="30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="24">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C37" s="24">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D37" s="24">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E37" s="24">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F37" s="24">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G37" s="24">
+        <v>0.6492</v>
+      </c>
+      <c r="H37" s="24">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="24">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C41" s="24">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D41" s="24">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E41" s="24">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F41" s="24">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G41" s="24">
+        <v>0.6492</v>
+      </c>
+      <c r="H41" s="24">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="25"/>
+      <c r="B42" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" s="5">
+        <v>0.60570000000000002</v>
+      </c>
+      <c r="C43" s="5">
+        <v>0.21940000000000001</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.40749999999999997</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.66769999999999996</v>
+      </c>
+      <c r="F43" s="5">
+        <v>0.61890000000000001</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0.62109999999999999</v>
+      </c>
+      <c r="H43" s="5">
+        <v>0.62849999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="B44" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="5">
+        <v>0.59660000000000002</v>
+      </c>
+      <c r="C45" s="5">
+        <v>0.2344</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.6129</v>
+      </c>
+      <c r="F45" s="5">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0.59509999999999996</v>
+      </c>
+      <c r="H45" s="5">
+        <v>0.60799999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="D46" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="5">
+        <v>0.60609999999999997</v>
+      </c>
+      <c r="C47" s="5">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="D47" s="5">
+        <v>0.43009999999999998</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="F47" s="5">
+        <v>0.62949999999999995</v>
+      </c>
+      <c r="G47" s="5">
+        <v>0.63319999999999999</v>
+      </c>
+      <c r="H47" s="5">
+        <v>0.63629999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="B48" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H48" s="14" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
-      <c r="A33" s="1" t="s">
+    <row r="49" spans="1:24">
+      <c r="A49" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B49" s="5">
         <v>0.61350000000000005</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C49" s="5">
         <v>0.26769999999999999</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D49" s="5">
         <v>0.43440000000000001</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E49" s="5">
         <v>0.63439999999999996</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F49" s="5">
         <v>0.63790000000000002</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G49" s="5">
         <v>0.63970000000000005</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H49" s="5">
         <v>0.64839999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
-      <c r="B34" s="14" t="s">
+    <row r="50" spans="1:24">
+      <c r="B50" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C50" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D50" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E50" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F50" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G50" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H50" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I50" s="29" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="3" customFormat="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" s="3" customFormat="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="8"/>
-      <c r="W36" s="8"/>
-      <c r="X36" s="8"/>
-    </row>
-    <row r="37" spans="1:24" s="3" customFormat="1">
-      <c r="A37" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="11">
-        <v>0.57450000000000001</v>
-      </c>
-      <c r="C37" s="10">
-        <v>0.24410000000000001</v>
-      </c>
-      <c r="D37" s="11">
-        <v>0.38529999999999998</v>
-      </c>
-      <c r="E37" s="11">
-        <v>0.5706</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-    </row>
-    <row r="38" spans="1:24" s="3" customFormat="1">
-      <c r="A38" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-    </row>
-    <row r="39" spans="1:24" s="3" customFormat="1">
-      <c r="A39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="10">
-        <v>0.59050000000000002</v>
-      </c>
-      <c r="C39" s="11">
-        <v>0.23530000000000001</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0.4118</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.60289999999999999</v>
-      </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-    </row>
-    <row r="40" spans="1:24" s="3" customFormat="1">
-      <c r="A40" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-    </row>
-    <row r="41" spans="1:24" s="3" customFormat="1">
-      <c r="A41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="5">
-        <v>0.59040000000000004</v>
-      </c>
-      <c r="C41" s="5">
-        <v>0.22189999999999999</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.41880000000000001</v>
-      </c>
-      <c r="E41" s="5">
-        <v>0.61560000000000004</v>
-      </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-    </row>
-    <row r="42" spans="1:24" s="3" customFormat="1">
-      <c r="A42" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-    </row>
-    <row r="43" spans="1:24" s="3" customFormat="1">
-      <c r="A43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="6">
-        <v>0.60450000000000004</v>
-      </c>
-      <c r="C43" s="6">
-        <v>0.24840000000000001</v>
-      </c>
-      <c r="D43" s="6">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.61880000000000002</v>
-      </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-    </row>
-    <row r="44" spans="1:24" s="3" customFormat="1">
-      <c r="A44" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-    </row>
-    <row r="45" spans="1:24" s="3" customFormat="1">
-      <c r="A45" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="22">
-        <v>0.59840000000000004</v>
-      </c>
-      <c r="C45" s="22">
-        <v>0.22869999999999999</v>
-      </c>
-      <c r="D45" s="22">
-        <v>0.42230000000000001</v>
-      </c>
-      <c r="E45" s="22">
-        <v>0.61580000000000001</v>
-      </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-    </row>
-    <row r="46" spans="1:24" s="3" customFormat="1">
-      <c r="A46" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-    </row>
-    <row r="47" spans="1:24">
-      <c r="A47" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="24">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C47" s="24">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D47" s="24">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E47" s="24">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:24">
-      <c r="A48" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" s="5">
-        <v>0.59119999999999995</v>
-      </c>
-      <c r="C49" s="5">
-        <v>0.2082</v>
-      </c>
-      <c r="D49" s="5">
-        <v>0.40820000000000001</v>
-      </c>
-      <c r="E49" s="5">
-        <v>0.60329999999999995</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="6">
-        <v>0.60209999999999997</v>
-      </c>
-      <c r="C51" s="6">
-        <v>0.2283</v>
-      </c>
-      <c r="D51" s="6">
-        <v>0.41089999999999999</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.63100000000000001</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>43</v>
-      </c>
+    <row r="51" spans="1:24" s="3" customFormat="1">
+      <c r="A51" s="4"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+    </row>
+    <row r="52" spans="1:24" s="3" customFormat="1">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="I52" s="1"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="8"/>
+      <c r="V52" s="8"/>
+      <c r="W52" s="8"/>
+      <c r="X52" s="8"/>
+    </row>
+    <row r="53" spans="1:24" s="3" customFormat="1">
       <c r="A53" s="9" t="s">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="B53" s="11">
-        <v>0.58909999999999996</v>
+        <v>0.57450000000000001</v>
       </c>
       <c r="C53" s="10">
-        <v>0.21490000000000001</v>
+        <v>0.24410000000000001</v>
       </c>
       <c r="D53" s="11">
-        <v>0.4032</v>
+        <v>0.38529999999999998</v>
       </c>
       <c r="E53" s="11">
-        <v>0.60719999999999996</v>
+        <v>0.5706</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+    </row>
+    <row r="54" spans="1:24" s="3" customFormat="1">
       <c r="A54" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" s="1"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+    </row>
+    <row r="55" spans="1:24" s="3" customFormat="1">
       <c r="A55" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="10">
-        <v>0.59489999999999998</v>
+        <v>0.59050000000000002</v>
       </c>
       <c r="C55" s="11">
-        <v>0.21160000000000001</v>
+        <v>0.23530000000000001</v>
       </c>
       <c r="D55" s="10">
-        <v>0.41039999999999999</v>
+        <v>0.4118</v>
       </c>
       <c r="E55" s="10">
-        <v>0.63370000000000004</v>
+        <v>0.60289999999999999</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+    </row>
+    <row r="56" spans="1:24" s="3" customFormat="1">
       <c r="A56" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+    </row>
+    <row r="57" spans="1:24" s="3" customFormat="1">
       <c r="A57" s="1" t="s">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="B57" s="5">
-        <v>0.59130000000000005</v>
-      </c>
-      <c r="C57" s="6">
-        <v>0.21640000000000001</v>
+        <v>0.59040000000000004</v>
+      </c>
+      <c r="C57" s="5">
+        <v>0.22189999999999999</v>
       </c>
       <c r="D57" s="5">
-        <v>0.40150000000000002</v>
+        <v>0.41880000000000001</v>
       </c>
       <c r="E57" s="5">
-        <v>0.6179</v>
+        <v>0.61560000000000004</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+    </row>
+    <row r="58" spans="1:24" s="3" customFormat="1">
       <c r="A58" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>17</v>
+        <v>118</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+    </row>
+    <row r="59" spans="1:24" s="3" customFormat="1">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B59" s="6">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="C59" s="5">
-        <v>0.2094</v>
+        <v>0.60450000000000004</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.24840000000000001</v>
       </c>
       <c r="D59" s="6">
-        <v>0.41089999999999999</v>
+        <v>0.43280000000000002</v>
       </c>
       <c r="E59" s="6">
-        <v>0.63580000000000003</v>
+        <v>0.61880000000000002</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="17" t="s">
-        <v>131</v>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+    </row>
+    <row r="60" spans="1:24" s="3" customFormat="1">
+      <c r="A60" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="9" t="s">
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+    </row>
+    <row r="61" spans="1:24" s="3" customFormat="1">
+      <c r="A61" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B61" s="11">
-        <v>0.59140000000000004</v>
-      </c>
-      <c r="C61" s="10">
-        <v>0.21759999999999999</v>
-      </c>
-      <c r="D61" s="10">
-        <v>0.39610000000000001</v>
-      </c>
-      <c r="E61" s="11">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="B61" s="22">
+        <v>0.59840000000000004</v>
+      </c>
+      <c r="C61" s="22">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="D61" s="22">
+        <v>0.42230000000000001</v>
+      </c>
+      <c r="E61" s="22">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>95</v>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+    </row>
+    <row r="62" spans="1:24" s="3" customFormat="1">
+      <c r="A62" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>120</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="9" t="s">
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+    </row>
+    <row r="63" spans="1:24">
+      <c r="A63" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="10">
-        <v>0.58919999999999995</v>
-      </c>
-      <c r="C63" s="11">
-        <v>0.2041</v>
-      </c>
-      <c r="D63" s="11">
-        <v>0.39169999999999999</v>
-      </c>
-      <c r="E63" s="10">
-        <v>0.62880000000000003</v>
+      <c r="B63" s="24">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C63" s="24">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D63" s="24">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E63" s="24">
+        <v>0.64729999999999999</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>17</v>
+    <row r="64" spans="1:24">
+      <c r="A64" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="5">
+        <v>0.59119999999999995</v>
+      </c>
+      <c r="C65" s="5">
+        <v>0.2082</v>
+      </c>
+      <c r="D65" s="5">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.60329999999999995</v>
+      </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:8">
+      <c r="A66" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B67" s="5">
-        <v>0.61270000000000002</v>
-      </c>
-      <c r="C67" s="5">
-        <v>0.26479999999999998</v>
-      </c>
-      <c r="D67" s="5">
-        <v>0.45619999999999999</v>
-      </c>
-      <c r="E67" s="5">
-        <v>0.64649999999999996</v>
-      </c>
-      <c r="F67" s="5">
-        <v>0.63890000000000002</v>
-      </c>
-      <c r="G67" s="5">
-        <v>0.64070000000000005</v>
-      </c>
-      <c r="H67" s="5">
-        <v>0.64470000000000005</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" s="22">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C68" s="22">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D68" s="22">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E68" s="22">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F68" s="22">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G68" s="22">
-        <v>0.6492</v>
-      </c>
-      <c r="H68" s="22">
-        <v>0.65200000000000002</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B69" s="5">
-        <v>0.6099</v>
-      </c>
-      <c r="C69" s="5">
-        <v>0.2495</v>
-      </c>
-      <c r="D69" s="5">
-        <v>0.44090000000000001</v>
-      </c>
-      <c r="E69" s="5">
-        <v>0.63439999999999996</v>
-      </c>
-      <c r="F69" s="5">
-        <v>0.64070000000000005</v>
-      </c>
-      <c r="G69" s="5">
-        <v>0.64610000000000001</v>
-      </c>
-      <c r="H69" s="5">
-        <v>0.64839999999999998</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B70" s="5">
-        <v>0.61339999999999995</v>
-      </c>
-      <c r="C70" s="5">
-        <v>0.2581</v>
-      </c>
-      <c r="D70" s="5">
-        <v>0.43959999999999999</v>
-      </c>
-      <c r="E70" s="5">
-        <v>0.65810000000000002</v>
-      </c>
-      <c r="F70" s="5">
-        <v>0.63619999999999999</v>
-      </c>
-      <c r="G70" s="5">
-        <v>0.63880000000000003</v>
-      </c>
-      <c r="H70" s="5">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B72" s="5">
-        <v>0.6119</v>
-      </c>
-      <c r="C72" s="5">
-        <v>0.2409</v>
-      </c>
-      <c r="D72" s="5">
-        <v>0.44190000000000002</v>
-      </c>
-      <c r="E72" s="5">
-        <v>0.63980000000000004</v>
-      </c>
-      <c r="F72" s="5">
-        <v>0.64159999999999995</v>
-      </c>
-      <c r="G72" s="5">
-        <v>0.64590000000000003</v>
-      </c>
-      <c r="H72" s="5">
-        <v>0.64239999999999997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B73" s="22">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C73" s="22">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D73" s="22">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E73" s="22">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F73" s="22">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G73" s="22">
-        <v>0.6492</v>
-      </c>
-      <c r="H73" s="22">
-        <v>0.65200000000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B74" s="5">
-        <v>0.61829999999999996</v>
-      </c>
-      <c r="C74" s="5">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="D74" s="5">
-        <v>0.45269999999999999</v>
-      </c>
-      <c r="E74" s="5">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="F74" s="5">
-        <v>0.64159999999999995</v>
-      </c>
-      <c r="G74" s="5">
-        <v>0.66190000000000004</v>
-      </c>
-      <c r="H74" s="5">
-        <v>0.65010000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="B67" s="6">
+        <v>0.60209999999999997</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.2283</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="11">
+        <v>0.58909999999999996</v>
+      </c>
+      <c r="C69" s="10">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0.4032</v>
+      </c>
+      <c r="E69" s="11">
+        <v>0.60719999999999996</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="10">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="C71" s="11">
+        <v>0.21160000000000001</v>
+      </c>
+      <c r="D71" s="10">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="E71" s="10">
+        <v>0.63370000000000004</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="5">
+        <v>0.59130000000000005</v>
+      </c>
+      <c r="C73" s="6">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="D73" s="5">
+        <v>0.40150000000000002</v>
+      </c>
+      <c r="E73" s="5">
+        <v>0.6179</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B75" s="5">
-        <v>0.60140000000000005</v>
+        <v>12</v>
+      </c>
+      <c r="B75" s="6">
+        <v>0.59499999999999997</v>
       </c>
       <c r="C75" s="5">
-        <v>0.26229999999999998</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0.45229999999999998</v>
-      </c>
-      <c r="E75" s="5">
-        <v>0.63980000000000004</v>
-      </c>
-      <c r="F75" s="5">
-        <v>0.63949999999999996</v>
-      </c>
-      <c r="G75" s="5">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="H75" s="5">
-        <v>0.65329999999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B76" s="5">
-        <v>0.60060000000000002</v>
-      </c>
-      <c r="C76" s="5">
-        <v>0.25159999999999999</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.44519999999999998</v>
-      </c>
-      <c r="E76" s="5">
+        <v>0.2094</v>
+      </c>
+      <c r="D75" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E75" s="6">
         <v>0.63580000000000003</v>
       </c>
-      <c r="F76" s="5">
-        <v>0.63770000000000004</v>
-      </c>
-      <c r="G76" s="5">
-        <v>0.63790000000000002</v>
-      </c>
-      <c r="H76" s="5">
-        <v>0.64980000000000004</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78" s="5">
-        <v>0.5877</v>
-      </c>
-      <c r="C78" s="5">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="D78" s="5">
-        <v>0.41399999999999998</v>
-      </c>
-      <c r="E78" s="5">
-        <v>0.60540000000000005</v>
-      </c>
-      <c r="F78" s="5">
-        <v>0.57179999999999997</v>
-      </c>
-      <c r="G78" s="5">
-        <v>0.59030000000000005</v>
-      </c>
-      <c r="H78" s="5">
-        <v>0.60409999999999997</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B79" s="5">
-        <v>0.61519999999999997</v>
-      </c>
-      <c r="C79" s="5">
-        <v>0.27529999999999999</v>
-      </c>
-      <c r="D79" s="5">
-        <v>0.46239999999999998</v>
-      </c>
-      <c r="E79" s="5">
-        <v>0.63439999999999996</v>
-      </c>
-      <c r="F79" s="5">
-        <v>0.63790000000000002</v>
-      </c>
-      <c r="G79" s="5">
-        <v>0.64339999999999997</v>
-      </c>
-      <c r="H79" s="5">
-        <v>0.64639999999999997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B80" s="22">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C80" s="22">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D80" s="22">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E80" s="22">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F80" s="22">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G80" s="22">
-        <v>0.6492</v>
-      </c>
-      <c r="H80" s="22">
-        <v>0.65200000000000002</v>
-      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="11">
+        <v>0.59140000000000004</v>
+      </c>
+      <c r="C77" s="10">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="D77" s="10">
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="E77" s="11">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="10">
+        <v>0.58919999999999995</v>
+      </c>
+      <c r="C79" s="11">
+        <v>0.2041</v>
+      </c>
+      <c r="D79" s="11">
+        <v>0.39169999999999999</v>
+      </c>
+      <c r="E79" s="10">
+        <v>0.62880000000000003</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B81" s="5">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="C81" s="5">
-        <v>0.27850000000000003</v>
-      </c>
-      <c r="D81" s="5">
-        <v>0.45379999999999998</v>
-      </c>
-      <c r="E81" s="5">
-        <v>0.64270000000000005</v>
-      </c>
-      <c r="F81" s="5">
-        <v>0.64659999999999995</v>
-      </c>
-      <c r="G81" s="5">
-        <v>0.64410000000000001</v>
-      </c>
-      <c r="H81" s="5">
-        <v>0.64910000000000001</v>
-      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B82" s="5">
-        <v>0.62519999999999998</v>
-      </c>
-      <c r="C82" s="5">
-        <v>0.27110000000000001</v>
-      </c>
-      <c r="D82" s="5">
-        <v>0.45119999999999999</v>
-      </c>
-      <c r="E82" s="5">
-        <v>0.64659999999999995</v>
-      </c>
-      <c r="F82" s="5">
-        <v>0.64290000000000003</v>
-      </c>
-      <c r="G82" s="5">
-        <v>0.64449999999999996</v>
-      </c>
-      <c r="H82" s="5">
-        <v>0.6502</v>
-      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B83" s="5">
-        <v>0.60870000000000002</v>
+        <v>0.61270000000000002</v>
       </c>
       <c r="C83" s="5">
-        <v>0.24729999999999999</v>
+        <v>0.26479999999999998</v>
       </c>
       <c r="D83" s="5">
-        <v>0.44729999999999998</v>
+        <v>0.45619999999999999</v>
       </c>
       <c r="E83" s="5">
-        <v>0.64410000000000001</v>
+        <v>0.64649999999999996</v>
       </c>
       <c r="F83" s="5">
-        <v>0.59709999999999996</v>
+        <v>0.63890000000000002</v>
       </c>
       <c r="G83" s="5">
-        <v>0.61409999999999998</v>
+        <v>0.64070000000000005</v>
       </c>
       <c r="H83" s="5">
-        <v>0.62350000000000005</v>
-      </c>
-      <c r="I83" s="29" t="s">
-        <v>146</v>
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="22">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C84" s="22">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D84" s="22">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E84" s="22">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F84" s="22">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G84" s="22">
+        <v>0.6492</v>
+      </c>
+      <c r="H84" s="22">
+        <v>0.65200000000000002</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B85" s="5">
-        <v>0.61519999999999997</v>
+        <v>0.6099</v>
       </c>
       <c r="C85" s="5">
-        <v>0.25380000000000003</v>
+        <v>0.2495</v>
       </c>
       <c r="D85" s="5">
-        <v>0.4516</v>
+        <v>0.44090000000000001</v>
       </c>
       <c r="E85" s="5">
-        <v>0.64549999999999996</v>
+        <v>0.63439999999999996</v>
       </c>
       <c r="F85" s="5">
-        <v>0.64600000000000002</v>
+        <v>0.64070000000000005</v>
       </c>
       <c r="G85" s="5">
-        <v>0.64539999999999997</v>
+        <v>0.64610000000000001</v>
       </c>
       <c r="H85" s="5">
-        <v>0.65049999999999997</v>
+        <v>0.64839999999999998</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B86" s="22">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C86" s="22">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D86" s="22">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E86" s="22">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F86" s="22">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G86" s="22">
-        <v>0.6492</v>
-      </c>
-      <c r="H86" s="22">
-        <v>0.65200000000000002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B87" s="5">
-        <v>0.61080000000000001</v>
-      </c>
-      <c r="C87" s="5">
-        <v>0.2676</v>
-      </c>
-      <c r="D87" s="5">
-        <v>0.4466</v>
-      </c>
-      <c r="E87" s="5">
-        <v>0.64549999999999996</v>
-      </c>
-      <c r="F87" s="5">
-        <v>0.64680000000000004</v>
-      </c>
-      <c r="G87" s="5">
-        <v>0.64810000000000001</v>
-      </c>
-      <c r="H87" s="5">
-        <v>0.65069999999999995</v>
+      <c r="A86" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" s="5">
+        <v>0.61339999999999995</v>
+      </c>
+      <c r="C86" s="5">
+        <v>0.2581</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0.43959999999999999</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.65810000000000002</v>
+      </c>
+      <c r="F86" s="5">
+        <v>0.63619999999999999</v>
+      </c>
+      <c r="G86" s="5">
+        <v>0.63880000000000003</v>
+      </c>
+      <c r="H86" s="5">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B88" s="5">
+        <v>0.6119</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.2409</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.44190000000000002</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.63980000000000004</v>
+      </c>
+      <c r="F88" s="5">
+        <v>0.64159999999999995</v>
+      </c>
+      <c r="G88" s="5">
+        <v>0.64590000000000003</v>
+      </c>
+      <c r="H88" s="5">
+        <v>0.64239999999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B89" s="22">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C89" s="22">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D89" s="22">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E89" s="22">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F89" s="22">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G89" s="22">
+        <v>0.6492</v>
+      </c>
+      <c r="H89" s="22">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="5">
+        <v>0.61829999999999996</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.45269999999999999</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="F90" s="5">
+        <v>0.64159999999999995</v>
+      </c>
+      <c r="G90" s="5">
+        <v>0.66190000000000004</v>
+      </c>
+      <c r="H90" s="5">
+        <v>0.65010000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" s="5">
+        <v>0.60140000000000005</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0.26229999999999998</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0.45229999999999998</v>
+      </c>
+      <c r="E91" s="5">
+        <v>0.63980000000000004</v>
+      </c>
+      <c r="F91" s="5">
+        <v>0.63949999999999996</v>
+      </c>
+      <c r="G91" s="5">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="H91" s="5">
+        <v>0.65329999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B92" s="5">
+        <v>0.60060000000000002</v>
+      </c>
+      <c r="C92" s="5">
+        <v>0.25159999999999999</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.44519999999999998</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.63580000000000003</v>
+      </c>
+      <c r="F92" s="5">
+        <v>0.63770000000000004</v>
+      </c>
+      <c r="G92" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="H92" s="5">
+        <v>0.64980000000000004</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B94" s="5">
+        <v>0.5877</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.60540000000000005</v>
+      </c>
+      <c r="F94" s="5">
+        <v>0.57179999999999997</v>
+      </c>
+      <c r="G94" s="5">
+        <v>0.59030000000000005</v>
+      </c>
+      <c r="H94" s="5">
+        <v>0.60409999999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B95" s="5">
+        <v>0.61519999999999997</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0.27529999999999999</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.46239999999999998</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F95" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0.64339999999999997</v>
+      </c>
+      <c r="H95" s="5">
+        <v>0.64639999999999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="22">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C96" s="22">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D96" s="22">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E96" s="22">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F96" s="22">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G96" s="22">
+        <v>0.6492</v>
+      </c>
+      <c r="H96" s="22">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B97" s="5">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="C97" s="5">
+        <v>0.27850000000000003</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.45379999999999998</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.64270000000000005</v>
+      </c>
+      <c r="F97" s="5">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="G97" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="H97" s="5">
+        <v>0.64910000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="5">
+        <v>0.62519999999999998</v>
+      </c>
+      <c r="C98" s="5">
+        <v>0.27110000000000001</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0.45119999999999999</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="F98" s="5">
+        <v>0.64290000000000003</v>
+      </c>
+      <c r="G98" s="5">
+        <v>0.64449999999999996</v>
+      </c>
+      <c r="H98" s="5">
+        <v>0.6502</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="5">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="C99" s="5">
+        <v>0.24729999999999999</v>
+      </c>
+      <c r="D99" s="5">
+        <v>0.44729999999999998</v>
+      </c>
+      <c r="E99" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F99" s="5">
+        <v>0.59709999999999996</v>
+      </c>
+      <c r="G99" s="5">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="H99" s="5">
+        <v>0.62350000000000005</v>
+      </c>
+      <c r="I99" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B101" s="5">
+        <v>0.61519999999999997</v>
+      </c>
+      <c r="C101" s="5">
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="D101" s="5">
+        <v>0.4516</v>
+      </c>
+      <c r="E101" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F101" s="5">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="G101" s="5">
+        <v>0.64539999999999997</v>
+      </c>
+      <c r="H101" s="5">
+        <v>0.65049999999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B102" s="22">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C102" s="22">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D102" s="22">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E102" s="22">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F102" s="22">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G102" s="22">
+        <v>0.6492</v>
+      </c>
+      <c r="H102" s="22">
+        <v>0.65200000000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B103" s="5">
+        <v>0.61080000000000001</v>
+      </c>
+      <c r="C103" s="5">
+        <v>0.2676</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0.4466</v>
+      </c>
+      <c r="E103" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F103" s="5">
+        <v>0.64680000000000004</v>
+      </c>
+      <c r="G103" s="5">
+        <v>0.64810000000000001</v>
+      </c>
+      <c r="H103" s="5">
+        <v>0.65069999999999995</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B104" s="5">
         <v>0.61029999999999995</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C104" s="5">
         <v>0.25590000000000002</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D104" s="5">
         <v>0.43759999999999999</v>
       </c>
-      <c r="E88" s="5">
+      <c r="E104" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F88" s="5">
+      <c r="F104" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G88" s="5">
+      <c r="G104" s="5">
         <v>0.64370000000000005</v>
       </c>
-      <c r="H88" s="5">
+      <c r="H104" s="5">
         <v>0.64970000000000006</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="1" t="s">
+    <row r="105" spans="1:9">
+      <c r="A105" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B105" s="5">
         <v>0.61360000000000003</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C105" s="5">
         <v>0.2591</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D105" s="5">
         <v>0.42370000000000002</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E105" s="5">
         <v>0.65590000000000004</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F105" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G105" s="5">
         <v>0.64149999999999996</v>
       </c>
-      <c r="H89" s="5">
+      <c r="H105" s="5">
         <v>0.64249999999999996</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E17BD77-C243-7B4B-BD1D-206E5F472AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EDB39D-FFF1-9A4E-9D81-4FE0B685669E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="199">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -837,6 +837,26 @@
   </si>
   <si>
     <t>TCI (LSTM-Tatt) rho=0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rolling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Roll Day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdaGrowth (LSTM-Tatt)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1018,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1099,6 +1119,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1381,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA91"/>
+  <dimension ref="A1:AA99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -3516,7 +3542,7 @@
         <v>0.40749999999999997</v>
       </c>
       <c r="E43" s="5">
-        <v>0.66769999999999996</v>
+        <v>0.62770000000000004</v>
       </c>
       <c r="F43" s="5">
         <v>0.61890000000000001</v>
@@ -4727,11 +4753,111 @@
       </c>
       <c r="I91" s="5"/>
     </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="18">
+        <v>0.59840000000000004</v>
+      </c>
+      <c r="C96" s="18">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="D96" s="18">
+        <v>0.42230000000000001</v>
+      </c>
+      <c r="E96" s="18">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="F96" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G96" s="18">
+        <v>0.62470000000000003</v>
+      </c>
+      <c r="H96" s="18">
+        <v>0.62729999999999997</v>
+      </c>
+      <c r="I96" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B97" s="20">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C97" s="20">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D97" s="20">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E97" s="20">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F97" s="20">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G97" s="20">
+        <v>0.6492</v>
+      </c>
+      <c r="H97" s="20">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I97" s="38"/>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="I98" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="I99" s="38"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="S1:Y1"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="I98:I99"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EDB39D-FFF1-9A4E-9D81-4FE0B685669E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F16595-87DA-7A41-A031-CA1208D84035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="201">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -844,19 +844,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Roll Day</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdaGrowth (LSTM-Tatt)</t>
+    <t>0.2361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6085</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5829</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1038,7 +1046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1121,10 +1129,14 @@
     <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4753,111 +4765,172 @@
       </c>
       <c r="I91" s="5"/>
     </row>
+    <row r="93" spans="1:10">
+      <c r="B93" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1" t="s">
-        <v>194</v>
+      <c r="B94" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="39">
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="D94" s="39">
+        <v>0.42049999999999998</v>
+      </c>
+      <c r="E94" s="39">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="F94" s="39">
+        <v>0.62319999999999998</v>
+      </c>
+      <c r="G94" s="39">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="H94" s="39">
+        <v>0.627</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I95" s="1" t="s">
+      <c r="B95" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" s="39">
+        <v>0.23219999999999999</v>
+      </c>
+      <c r="D95" s="39">
+        <v>0.41930000000000001</v>
+      </c>
+      <c r="E95" s="39">
+        <v>0.61980000000000002</v>
+      </c>
+      <c r="F95" s="39">
+        <v>0.61890000000000001</v>
+      </c>
+      <c r="G95" s="39">
+        <v>0.62019999999999997</v>
+      </c>
+      <c r="H95" s="39">
+        <v>0.62670000000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="B96" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C96" s="39">
+        <v>0.2432</v>
+      </c>
+      <c r="D96" s="39">
+        <v>0.41320000000000001</v>
+      </c>
+      <c r="E96" s="39">
+        <v>0.59550000000000003</v>
+      </c>
+      <c r="F96" s="39">
+        <v>0.62470000000000003</v>
+      </c>
+      <c r="G96" s="39">
+        <v>0.63060000000000005</v>
+      </c>
+      <c r="H96" s="39">
+        <v>0.63339999999999996</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8">
+      <c r="B97" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C97" s="39">
+        <v>0.2218</v>
+      </c>
+      <c r="D97" s="39">
+        <v>0.40479999999999999</v>
+      </c>
+      <c r="E97" s="39">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="F97" s="39">
+        <v>0.59419999999999995</v>
+      </c>
+      <c r="G97" s="39">
+        <v>0.59850000000000003</v>
+      </c>
+      <c r="H97" s="39">
+        <v>0.60119999999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8">
+      <c r="B98" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C98" s="40" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="18">
-        <v>0.59840000000000004</v>
-      </c>
-      <c r="C96" s="18">
-        <v>0.22869999999999999</v>
-      </c>
-      <c r="D96" s="18">
-        <v>0.42230000000000001</v>
-      </c>
-      <c r="E96" s="18">
-        <v>0.61580000000000001</v>
-      </c>
-      <c r="F96" s="18">
-        <v>0.625</v>
-      </c>
-      <c r="G96" s="18">
-        <v>0.62470000000000003</v>
-      </c>
-      <c r="H96" s="18">
-        <v>0.62729999999999997</v>
-      </c>
-      <c r="I96" s="39" t="s">
+      <c r="D98" s="40" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="17" t="s">
+      <c r="E98" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="F98" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="G98" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="B97" s="20">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C97" s="20">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D97" s="20">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E97" s="20">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F97" s="20">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G97" s="20">
-        <v>0.6492</v>
-      </c>
-      <c r="H97" s="20">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I97" s="38"/>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="I98" s="39" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="I99" s="38"/>
+      <c r="H98" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8">
+      <c r="B99" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C99" s="41">
+        <v>0.27739999999999998</v>
+      </c>
+      <c r="D99" s="41">
+        <v>0.4496</v>
+      </c>
+      <c r="E99" s="41">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F99" s="41">
+        <v>0.6421</v>
+      </c>
+      <c r="G99" s="41">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="H99" s="41">
+        <v>0.64980000000000004</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="S1:Y1"/>
-    <mergeCell ref="I96:I97"/>
-    <mergeCell ref="I98:I99"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/RaisingTSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F16595-87DA-7A41-A031-CA1208D84035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F29DF6-33EE-4A4D-92C4-E64E0EC3B9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="212">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -865,6 +865,50 @@
   </si>
   <si>
     <t>0.5829</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5529</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3650</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5798</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5833</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5895</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandChoice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.059)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0.052)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1046,7 +1090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1127,16 +1171,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1419,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA99"/>
+  <dimension ref="A1:AA102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1547,10 +1581,10 @@
         <v>0.56040000000000001</v>
       </c>
       <c r="C3" s="11">
-        <v>0.23549999999999999</v>
+        <v>0.2155</v>
       </c>
       <c r="D3" s="11">
-        <v>0.39889999999999998</v>
+        <v>0.37890000000000001</v>
       </c>
       <c r="E3" s="11">
         <v>0.56769999999999998</v>
@@ -1711,7 +1745,7 @@
       </c>
       <c r="I5" s="10">
         <f>AVERAGE(B5:H5)/AVERAGE(B3:H3)</f>
-        <v>1.0433111154133363</v>
+        <v>1.0549822412394776</v>
       </c>
       <c r="K5" s="10">
         <v>0.56710000000000005</v>
@@ -1846,10 +1880,10 @@
         <v>0.58279999999999998</v>
       </c>
       <c r="F7" s="5">
-        <v>0.66810000000000003</v>
+        <v>0.64810000000000001</v>
       </c>
       <c r="G7" s="5">
-        <v>0.66300000000000003</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="H7" s="5">
         <v>0.65810000000000002</v>
@@ -1997,7 +2031,7 @@
       </c>
       <c r="I9" s="10">
         <f>AVERAGE(B9:H9)/AVERAGE(B7:H7)</f>
-        <v>1.0230558096980789</v>
+        <v>1.0322299881313464</v>
       </c>
       <c r="K9" s="6">
         <v>0.61370000000000002</v>
@@ -2684,10 +2718,10 @@
         <v>0.21940000000000001</v>
       </c>
       <c r="D19" s="11">
-        <v>0.40649999999999997</v>
+        <v>0.40050000000000002</v>
       </c>
       <c r="E19" s="11">
-        <v>0.63549999999999995</v>
+        <v>0.61950000000000005</v>
       </c>
       <c r="F19" s="11">
         <v>0.59489999999999998</v>
@@ -2757,7 +2791,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>141</v>
@@ -2836,11 +2870,11 @@
         <v>0.61809999999999998</v>
       </c>
       <c r="H21" s="10">
-        <v>0.62529999999999997</v>
+        <v>0.62970000000000004</v>
       </c>
       <c r="I21" s="10">
         <f>AVERAGE(B21:H21)/AVERAGE(B19:H19)</f>
-        <v>1.021877377975867</v>
+        <v>1.029226815398075</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="10">
@@ -3279,185 +3313,184 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B33" s="5">
-        <v>0.56430000000000002</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0.2205</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.40749999999999997</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0.59730000000000005</v>
-      </c>
-      <c r="G33" s="5">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="H33" s="5">
-        <v>0.60040000000000004</v>
-      </c>
-      <c r="I33" s="5"/>
+        <v>201</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="I33" s="14"/>
+      <c r="J33" s="23"/>
       <c r="L33" s="1">
-        <f>C33*1065*2-160</f>
+        <f>C35*1065*2-160</f>
         <v>309.66500000000002</v>
       </c>
       <c r="M33" s="1">
-        <f>D33*1065*2-320</f>
+        <f>D35*1065*2-320</f>
         <v>547.97499999999991</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="B34" s="14" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I34" s="14"/>
-      <c r="J34" s="24"/>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>156</v>
+        <v>148</v>
+      </c>
+      <c r="B35" s="5">
+        <v>0.56430000000000002</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0.2205</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.40749999999999997</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="F35" s="5">
+        <v>0.59730000000000005</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="H35" s="5">
+        <v>0.60040000000000004</v>
       </c>
       <c r="I35" s="5"/>
       <c r="L35" s="1">
-        <f>C35*1065*2-160</f>
+        <f>C37*1065*2-160</f>
         <v>332.66900000000004</v>
       </c>
       <c r="M35" s="1">
-        <f>D35*1065*2-320</f>
+        <f>D37*1065*2-320</f>
         <v>529.01800000000003</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="B36" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="24"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="20">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C37" s="20">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D37" s="20">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E37" s="20">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F37" s="20">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G37" s="20">
-        <v>0.6492</v>
-      </c>
-      <c r="H37" s="20">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>166</v>
-      </c>
+      <c r="A37" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I37" s="5"/>
       <c r="L37" s="1">
-        <f>C37*1065*2-160</f>
+        <f>C39*1065*2-160</f>
         <v>435.548</v>
       </c>
       <c r="M37" s="1">
-        <f>D37*1065*2-320</f>
+        <f>D39*1065*2-320</f>
         <v>639.56500000000005</v>
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="22" t="s">
+      <c r="B38" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="G38" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="22"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="24"/>
       <c r="L38" s="1">
         <f>L37/L29</f>
         <v>1.2001377733077996</v>
@@ -3468,14 +3501,33 @@
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
+      <c r="A39" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="20">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C39" s="20">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E39" s="20">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F39" s="20">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G39" s="20">
+        <v>0.6492</v>
+      </c>
+      <c r="H39" s="20">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>166</v>
+      </c>
       <c r="L39" s="1" t="s">
         <v>181</v>
       </c>
@@ -3484,384 +3536,363 @@
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I40" s="22"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="17" t="s">
+    <row r="43" spans="1:13">
+      <c r="A43" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B43" s="20">
         <v>0.62370000000000003</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C43" s="20">
         <v>0.27960000000000002</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D43" s="20">
         <v>0.45050000000000001</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E43" s="20">
         <v>0.64729999999999999</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F43" s="20">
         <v>0.64880000000000004</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G43" s="20">
         <v>0.6492</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H43" s="20">
         <v>0.65200000000000002</v>
       </c>
-      <c r="I41" s="20"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="21"/>
-      <c r="B42" s="22" t="s">
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="21"/>
+      <c r="B44" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C44" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D44" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="E44" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="22" t="s">
+      <c r="F44" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G44" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="H42" s="22" t="s">
+      <c r="H44" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="I42" s="22"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B43" s="5">
-        <v>0.60570000000000002</v>
-      </c>
-      <c r="C43" s="5">
-        <v>0.21940000000000001</v>
-      </c>
-      <c r="D43" s="5">
-        <v>0.40749999999999997</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.62770000000000004</v>
-      </c>
-      <c r="F43" s="5">
-        <v>0.61890000000000001</v>
-      </c>
-      <c r="G43" s="5">
-        <v>0.62109999999999999</v>
-      </c>
-      <c r="H43" s="5">
-        <v>0.62849999999999995</v>
-      </c>
-      <c r="I43" s="5"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="B44" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="I44" s="14"/>
+      <c r="I44" s="22"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="5">
-        <v>0.59660000000000002</v>
+        <v>0.60570000000000002</v>
       </c>
       <c r="C45" s="5">
-        <v>0.2344</v>
+        <v>0.21940000000000001</v>
       </c>
       <c r="D45" s="5">
-        <v>0.42580000000000001</v>
+        <v>0.40749999999999997</v>
       </c>
       <c r="E45" s="5">
-        <v>0.6129</v>
+        <v>0.62770000000000004</v>
       </c>
       <c r="F45" s="5">
-        <v>0.57399999999999995</v>
+        <v>0.61890000000000001</v>
       </c>
       <c r="G45" s="5">
-        <v>0.59509999999999996</v>
+        <v>0.62109999999999999</v>
       </c>
       <c r="H45" s="5">
-        <v>0.60799999999999998</v>
+        <v>0.62849999999999995</v>
       </c>
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:13">
       <c r="B46" s="14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="I46" s="14"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B47" s="5">
-        <v>0.60609999999999997</v>
+        <v>0.59660000000000002</v>
       </c>
       <c r="C47" s="5">
-        <v>0.25700000000000001</v>
+        <v>0.2344</v>
       </c>
       <c r="D47" s="5">
-        <v>0.43009999999999998</v>
+        <v>0.42580000000000001</v>
       </c>
       <c r="E47" s="5">
-        <v>0.62370000000000003</v>
+        <v>0.6129</v>
       </c>
       <c r="F47" s="5">
-        <v>0.62949999999999995</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="G47" s="5">
-        <v>0.63319999999999999</v>
+        <v>0.59509999999999996</v>
       </c>
       <c r="H47" s="5">
-        <v>0.63629999999999998</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:13">
       <c r="B48" s="14" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I48" s="14"/>
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" s="5">
-        <v>0.61350000000000005</v>
+        <v>0.60609999999999997</v>
       </c>
       <c r="C49" s="5">
-        <v>0.26769999999999999</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="D49" s="5">
-        <v>0.43440000000000001</v>
+        <v>0.43009999999999998</v>
       </c>
       <c r="E49" s="5">
-        <v>0.63439999999999996</v>
+        <v>0.62370000000000003</v>
       </c>
       <c r="F49" s="5">
-        <v>0.63790000000000002</v>
+        <v>0.62949999999999995</v>
       </c>
       <c r="G49" s="5">
-        <v>0.63970000000000005</v>
+        <v>0.63319999999999999</v>
       </c>
       <c r="H49" s="5">
-        <v>0.64839999999999998</v>
+        <v>0.63629999999999998</v>
       </c>
       <c r="I49" s="5"/>
-      <c r="J49" s="1" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="50" spans="1:25">
       <c r="B50" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="I50" s="14"/>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="5">
+        <v>0.61350000000000005</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.26769999999999999</v>
+      </c>
+      <c r="D51" s="5">
+        <v>0.43440000000000001</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F51" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0.63970000000000005</v>
+      </c>
+      <c r="H51" s="5">
+        <v>0.64839999999999998</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="B52" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C52" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D52" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E52" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F52" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G52" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H52" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="23" t="s">
+      <c r="I52" s="14"/>
+      <c r="J52" s="23" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:25" s="3" customFormat="1">
-      <c r="A51" s="4"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-    </row>
-    <row r="52" spans="1:25" s="3" customFormat="1">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="8"/>
-      <c r="W52" s="8"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="8"/>
-    </row>
-    <row r="53" spans="1:25" s="3" customFormat="1">
-      <c r="A53" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="11">
-        <v>0.57450000000000001</v>
-      </c>
-      <c r="D53" s="11">
-        <v>0.23530000000000001</v>
-      </c>
-      <c r="E53" s="11">
-        <v>0.38529999999999998</v>
-      </c>
-      <c r="F53" s="11">
-        <v>0.5706</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
+    <row r="53" spans="1:25">
+      <c r="A53" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="5">
+        <v>0.54830000000000001</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0.2011</v>
+      </c>
+      <c r="D53" s="5">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.56130000000000002</v>
+      </c>
+      <c r="F53" s="5">
+        <v>0.54479999999999995</v>
+      </c>
+      <c r="G53" s="5">
+        <v>0.55640000000000001</v>
+      </c>
+      <c r="H53" s="5">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="I53" s="14"/>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="1:25" s="3" customFormat="1">
-      <c r="A54" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="10">
-        <v>0.59050000000000002</v>
-      </c>
-      <c r="D54" s="10">
-        <v>0.24410000000000001</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0.4118</v>
-      </c>
-      <c r="F54" s="10">
-        <v>0.60289999999999999</v>
-      </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3870,70 +3901,58 @@
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
     </row>
     <row r="55" spans="1:25" s="3" customFormat="1">
-      <c r="A55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="5">
-        <v>0.59040000000000004</v>
-      </c>
-      <c r="D55" s="5">
-        <v>0.22189999999999999</v>
-      </c>
-      <c r="E55" s="5">
-        <v>0.41880000000000001</v>
-      </c>
-      <c r="F55" s="5">
-        <v>0.61560000000000004</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="S55" s="8"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="8"/>
+      <c r="W55" s="8"/>
+      <c r="X55" s="8"/>
+      <c r="Y55" s="8"/>
     </row>
     <row r="56" spans="1:25" s="3" customFormat="1">
-      <c r="A56" s="1" t="s">
-        <v>12</v>
+      <c r="A56" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C56" s="6">
-        <v>0.60450000000000004</v>
-      </c>
-      <c r="D56" s="6">
-        <v>0.24840000000000001</v>
-      </c>
-      <c r="E56" s="6">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="F56" s="6">
-        <v>0.63880000000000003</v>
+        <v>183</v>
+      </c>
+      <c r="C56" s="11">
+        <v>0.57450000000000001</v>
+      </c>
+      <c r="D56" s="11">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0.38529999999999998</v>
+      </c>
+      <c r="F56" s="11">
+        <v>0.5706</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3955,23 +3974,23 @@
       <c r="Y56" s="1"/>
     </row>
     <row r="57" spans="1:25" s="3" customFormat="1">
-      <c r="A57" s="17" t="s">
-        <v>3</v>
+      <c r="A57" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C57" s="18">
-        <v>0.59840000000000004</v>
-      </c>
-      <c r="D57" s="18">
-        <v>0.22869999999999999</v>
-      </c>
-      <c r="E57" s="18">
-        <v>0.42230000000000001</v>
-      </c>
-      <c r="F57" s="18">
-        <v>0.61580000000000001</v>
+        <v>183</v>
+      </c>
+      <c r="C57" s="10">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="D57" s="10">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.4118</v>
+      </c>
+      <c r="F57" s="10">
+        <v>0.60289999999999999</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3984,124 +4003,169 @@
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-    </row>
-    <row r="58" spans="1:25">
-      <c r="A58" s="17" t="s">
-        <v>12</v>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+    </row>
+    <row r="58" spans="1:25" s="3" customFormat="1">
+      <c r="A58" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C58" s="20">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="D58" s="20">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="E58" s="20">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="F58" s="20">
-        <v>0.64729999999999999</v>
+        <v>184</v>
+      </c>
+      <c r="C58" s="5">
+        <v>0.59040000000000004</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.41880000000000001</v>
+      </c>
+      <c r="F58" s="5">
+        <v>0.61560000000000004</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:25">
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+    </row>
+    <row r="59" spans="1:25" s="3" customFormat="1">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C59" s="5">
-        <v>0.59119999999999995</v>
-      </c>
-      <c r="D59" s="5">
-        <v>0.2082</v>
-      </c>
-      <c r="E59" s="5">
-        <v>0.40820000000000001</v>
-      </c>
-      <c r="F59" s="5">
-        <v>0.60329999999999995</v>
+        <v>184</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.60450000000000004</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.24840000000000001</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0.63880000000000003</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="1:25">
-      <c r="A60" s="1" t="s">
-        <v>12</v>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+    </row>
+    <row r="60" spans="1:25" s="3" customFormat="1">
+      <c r="A60" s="17" t="s">
+        <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C60" s="6">
-        <v>0.60209999999999997</v>
-      </c>
-      <c r="D60" s="6">
-        <v>0.2283</v>
-      </c>
-      <c r="E60" s="6">
-        <v>0.4209</v>
-      </c>
-      <c r="F60" s="6">
-        <v>0.63100000000000001</v>
+        <v>185</v>
+      </c>
+      <c r="C60" s="18">
+        <v>0.59840000000000004</v>
+      </c>
+      <c r="D60" s="18">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="E60" s="18">
+        <v>0.42230000000000001</v>
+      </c>
+      <c r="F60" s="18">
+        <v>0.61580000000000001</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
     </row>
     <row r="61" spans="1:25">
-      <c r="A61" s="9" t="s">
-        <v>3</v>
+      <c r="A61" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C61" s="11">
-        <v>0.58909999999999996</v>
-      </c>
-      <c r="D61" s="10">
-        <v>0.21490000000000001</v>
-      </c>
-      <c r="E61" s="11">
-        <v>0.4032</v>
-      </c>
-      <c r="F61" s="11">
-        <v>0.60719999999999996</v>
+        <v>185</v>
+      </c>
+      <c r="C61" s="20">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="D61" s="20">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="E61" s="20">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="F61" s="20">
+        <v>0.64729999999999999</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:25">
-      <c r="A62" s="9" t="s">
-        <v>12</v>
+      <c r="A62" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C62" s="10">
-        <v>0.59489999999999998</v>
-      </c>
-      <c r="D62" s="11">
-        <v>0.21160000000000001</v>
-      </c>
-      <c r="E62" s="10">
-        <v>0.41039999999999999</v>
-      </c>
-      <c r="F62" s="10">
-        <v>0.63370000000000004</v>
+        <v>186</v>
+      </c>
+      <c r="C62" s="5">
+        <v>0.59119999999999995</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0.2082</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="F62" s="5">
+        <v>0.60329999999999995</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -4109,45 +4173,45 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C63" s="5">
-        <v>0.59130000000000005</v>
+        <v>186</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.60209999999999997</v>
       </c>
       <c r="D63" s="6">
-        <v>0.2122</v>
-      </c>
-      <c r="E63" s="5">
-        <v>0.40150000000000002</v>
-      </c>
-      <c r="F63" s="5">
-        <v>0.6179</v>
+        <v>0.2283</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.4209</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0.63100000000000001</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:25">
-      <c r="A64" s="1" t="s">
-        <v>12</v>
+      <c r="A64" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C64" s="6">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="D64" s="5">
-        <v>0.2094</v>
-      </c>
-      <c r="E64" s="6">
-        <v>0.41089999999999999</v>
-      </c>
-      <c r="F64" s="6">
-        <v>0.63580000000000003</v>
+        <v>187</v>
+      </c>
+      <c r="C64" s="11">
+        <v>0.58909999999999996</v>
+      </c>
+      <c r="D64" s="10">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="E64" s="11">
+        <v>0.4032</v>
+      </c>
+      <c r="F64" s="11">
+        <v>0.60719999999999996</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -4155,774 +4219,843 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="9" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="11">
-        <v>0.59140000000000004</v>
-      </c>
-      <c r="D65" s="10">
-        <v>0.21759999999999999</v>
+        <v>187</v>
+      </c>
+      <c r="C65" s="10">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0.21160000000000001</v>
       </c>
       <c r="E65" s="10">
-        <v>0.39610000000000001</v>
-      </c>
-      <c r="F65" s="11">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>112</v>
-      </c>
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="F65" s="10">
+        <v>0.63370000000000004</v>
+      </c>
+      <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="9" t="s">
-        <v>12</v>
+      <c r="A66" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C66" s="10">
-        <v>0.58919999999999995</v>
-      </c>
-      <c r="D66" s="11">
-        <v>0.2041</v>
-      </c>
-      <c r="E66" s="11">
-        <v>0.39169999999999999</v>
-      </c>
-      <c r="F66" s="10">
-        <v>0.62880000000000003</v>
+        <v>188</v>
+      </c>
+      <c r="C66" s="5">
+        <v>0.59130000000000005</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0.2122</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.40150000000000002</v>
+      </c>
+      <c r="F66" s="5">
+        <v>0.6179</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="F67" s="4"/>
+      <c r="A67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.2094</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0.63580000000000003</v>
+      </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="A68" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" s="11">
+        <v>0.59140000000000004</v>
+      </c>
+      <c r="D68" s="10">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="E68" s="10">
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="F68" s="11">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B69" s="5">
-        <v>0.61270000000000002</v>
-      </c>
-      <c r="C69" s="5">
-        <v>0.26479999999999998</v>
-      </c>
-      <c r="D69" s="5">
-        <v>0.45619999999999999</v>
-      </c>
-      <c r="E69" s="5">
-        <v>0.64649999999999996</v>
-      </c>
-      <c r="F69" s="5">
-        <v>0.63890000000000002</v>
-      </c>
-      <c r="G69" s="5">
-        <v>0.64070000000000005</v>
-      </c>
-      <c r="H69" s="5">
-        <v>0.64470000000000005</v>
-      </c>
-      <c r="I69" s="5"/>
-      <c r="J69" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="A69" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="10">
+        <v>0.58919999999999995</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0.2041</v>
+      </c>
+      <c r="E69" s="11">
+        <v>0.39169999999999999</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0.62880000000000003</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B70" s="18">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C70" s="18">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D70" s="18">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E70" s="18">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F70" s="18">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G70" s="18">
-        <v>0.6492</v>
-      </c>
-      <c r="H70" s="18">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I70" s="18"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B71" s="5">
-        <v>0.6099</v>
-      </c>
-      <c r="C71" s="5">
-        <v>0.2495</v>
-      </c>
-      <c r="D71" s="5">
-        <v>0.44090000000000001</v>
-      </c>
-      <c r="E71" s="5">
-        <v>0.63439999999999996</v>
-      </c>
-      <c r="F71" s="5">
-        <v>0.64070000000000005</v>
-      </c>
-      <c r="G71" s="5">
-        <v>0.64610000000000001</v>
-      </c>
-      <c r="H71" s="5">
-        <v>0.64839999999999998</v>
-      </c>
-      <c r="I71" s="5"/>
-      <c r="J71" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B72" s="5">
-        <v>0.61339999999999995</v>
+        <v>0.61270000000000002</v>
       </c>
       <c r="C72" s="5">
-        <v>0.2581</v>
+        <v>0.26479999999999998</v>
       </c>
       <c r="D72" s="5">
-        <v>0.43959999999999999</v>
+        <v>0.45619999999999999</v>
       </c>
       <c r="E72" s="5">
-        <v>0.65810000000000002</v>
+        <v>0.64649999999999996</v>
       </c>
       <c r="F72" s="5">
-        <v>0.63619999999999999</v>
+        <v>0.63890000000000002</v>
       </c>
       <c r="G72" s="5">
-        <v>0.63880000000000003</v>
+        <v>0.64070000000000005</v>
       </c>
       <c r="H72" s="5">
-        <v>0.64500000000000002</v>
+        <v>0.64470000000000005</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" s="18">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C73" s="18">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D73" s="18">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E73" s="18">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F73" s="18">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G73" s="18">
+        <v>0.6492</v>
+      </c>
+      <c r="H73" s="18">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I73" s="18"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B74" s="5">
-        <v>0.6119</v>
+        <v>0.6099</v>
       </c>
       <c r="C74" s="5">
-        <v>0.2409</v>
+        <v>0.2495</v>
       </c>
       <c r="D74" s="5">
-        <v>0.44190000000000002</v>
+        <v>0.44090000000000001</v>
       </c>
       <c r="E74" s="5">
-        <v>0.63980000000000004</v>
+        <v>0.63439999999999996</v>
       </c>
       <c r="F74" s="5">
-        <v>0.64159999999999995</v>
+        <v>0.64070000000000005</v>
       </c>
       <c r="G74" s="5">
-        <v>0.64590000000000003</v>
+        <v>0.64610000000000001</v>
       </c>
       <c r="H74" s="5">
-        <v>0.64239999999999997</v>
+        <v>0.64839999999999998</v>
       </c>
       <c r="I74" s="5"/>
+      <c r="J74" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B75" s="18">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C75" s="18">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D75" s="18">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E75" s="18">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F75" s="18">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G75" s="18">
-        <v>0.6492</v>
-      </c>
-      <c r="H75" s="18">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I75" s="18"/>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B76" s="5">
-        <v>0.61829999999999996</v>
-      </c>
-      <c r="C76" s="5">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.45269999999999999</v>
-      </c>
-      <c r="E76" s="5">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="F76" s="5">
-        <v>0.64159999999999995</v>
-      </c>
-      <c r="G76" s="5">
-        <v>0.66190000000000004</v>
-      </c>
-      <c r="H76" s="5">
-        <v>0.65010000000000001</v>
-      </c>
-      <c r="I76" s="5"/>
+      <c r="A75" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B75" s="5">
+        <v>0.61339999999999995</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0.2581</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.43959999999999999</v>
+      </c>
+      <c r="E75" s="5">
+        <v>0.65810000000000002</v>
+      </c>
+      <c r="F75" s="5">
+        <v>0.63619999999999999</v>
+      </c>
+      <c r="G75" s="5">
+        <v>0.63880000000000003</v>
+      </c>
+      <c r="H75" s="5">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="I75" s="5"/>
+      <c r="J75" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B77" s="5">
-        <v>0.60140000000000005</v>
+        <v>0.6119</v>
       </c>
       <c r="C77" s="5">
-        <v>0.26229999999999998</v>
+        <v>0.2409</v>
       </c>
       <c r="D77" s="5">
-        <v>0.45229999999999998</v>
+        <v>0.44190000000000002</v>
       </c>
       <c r="E77" s="5">
         <v>0.63980000000000004</v>
       </c>
       <c r="F77" s="5">
-        <v>0.63949999999999996</v>
+        <v>0.64159999999999995</v>
       </c>
       <c r="G77" s="5">
-        <v>0.66300000000000003</v>
+        <v>0.64590000000000003</v>
       </c>
       <c r="H77" s="5">
-        <v>0.65329999999999999</v>
+        <v>0.64239999999999997</v>
       </c>
       <c r="I77" s="5"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" s="5">
-        <v>0.60060000000000002</v>
-      </c>
-      <c r="C78" s="5">
-        <v>0.25159999999999999</v>
-      </c>
-      <c r="D78" s="5">
-        <v>0.44519999999999998</v>
-      </c>
-      <c r="E78" s="5">
-        <v>0.63580000000000003</v>
-      </c>
-      <c r="F78" s="5">
-        <v>0.63770000000000004</v>
-      </c>
-      <c r="G78" s="5">
-        <v>0.63790000000000002</v>
-      </c>
-      <c r="H78" s="5">
-        <v>0.64980000000000004</v>
-      </c>
-      <c r="I78" s="5"/>
+      <c r="A78" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B78" s="18">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C78" s="18">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D78" s="18">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E78" s="18">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F78" s="18">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G78" s="18">
+        <v>0.6492</v>
+      </c>
+      <c r="H78" s="18">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I78" s="18"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="5">
+        <v>0.61829999999999996</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="D79" s="5">
+        <v>0.45269999999999999</v>
+      </c>
+      <c r="E79" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="F79" s="5">
+        <v>0.64159999999999995</v>
+      </c>
+      <c r="G79" s="5">
+        <v>0.66190000000000004</v>
+      </c>
+      <c r="H79" s="5">
+        <v>0.65010000000000001</v>
+      </c>
+      <c r="I79" s="5"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B80" s="5">
-        <v>0.5877</v>
+        <v>0.60140000000000005</v>
       </c>
       <c r="C80" s="5">
-        <v>0.24299999999999999</v>
+        <v>0.26229999999999998</v>
       </c>
       <c r="D80" s="5">
-        <v>0.41399999999999998</v>
+        <v>0.45229999999999998</v>
       </c>
       <c r="E80" s="5">
-        <v>0.60540000000000005</v>
+        <v>0.63980000000000004</v>
       </c>
       <c r="F80" s="5">
-        <v>0.57179999999999997</v>
+        <v>0.63949999999999996</v>
       </c>
       <c r="G80" s="5">
-        <v>0.59030000000000005</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="H80" s="5">
-        <v>0.60409999999999997</v>
+        <v>0.65329999999999999</v>
       </c>
       <c r="I80" s="5"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B81" s="5">
-        <v>0.61519999999999997</v>
+        <v>0.60060000000000002</v>
       </c>
       <c r="C81" s="5">
-        <v>0.27529999999999999</v>
+        <v>0.25159999999999999</v>
       </c>
       <c r="D81" s="5">
-        <v>0.46239999999999998</v>
+        <v>0.44519999999999998</v>
       </c>
       <c r="E81" s="5">
-        <v>0.63439999999999996</v>
+        <v>0.63580000000000003</v>
       </c>
       <c r="F81" s="5">
+        <v>0.63770000000000004</v>
+      </c>
+      <c r="G81" s="5">
         <v>0.63790000000000002</v>
       </c>
-      <c r="G81" s="5">
-        <v>0.64339999999999997</v>
-      </c>
       <c r="H81" s="5">
-        <v>0.64639999999999997</v>
+        <v>0.64980000000000004</v>
       </c>
       <c r="I81" s="5"/>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B82" s="18">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C82" s="18">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D82" s="18">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E82" s="18">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F82" s="18">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G82" s="18">
-        <v>0.6492</v>
-      </c>
-      <c r="H82" s="18">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I82" s="18"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B83" s="5">
-        <v>0.61799999999999999</v>
+        <v>0.5877</v>
       </c>
       <c r="C83" s="5">
-        <v>0.27850000000000003</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="D83" s="5">
-        <v>0.45379999999999998</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="E83" s="5">
-        <v>0.64270000000000005</v>
+        <v>0.60540000000000005</v>
       </c>
       <c r="F83" s="5">
-        <v>0.64659999999999995</v>
+        <v>0.57179999999999997</v>
       </c>
       <c r="G83" s="5">
-        <v>0.64410000000000001</v>
+        <v>0.59030000000000005</v>
       </c>
       <c r="H83" s="5">
-        <v>0.64910000000000001</v>
+        <v>0.60409999999999997</v>
       </c>
       <c r="I83" s="5"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B84" s="5">
-        <v>0.62519999999999998</v>
+        <v>0.61519999999999997</v>
       </c>
       <c r="C84" s="5">
-        <v>0.27110000000000001</v>
+        <v>0.27529999999999999</v>
       </c>
       <c r="D84" s="5">
-        <v>0.45119999999999999</v>
+        <v>0.46239999999999998</v>
       </c>
       <c r="E84" s="5">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="F84" s="5">
+        <v>0.63790000000000002</v>
+      </c>
+      <c r="G84" s="5">
+        <v>0.64339999999999997</v>
+      </c>
+      <c r="H84" s="5">
+        <v>0.64639999999999997</v>
+      </c>
+      <c r="I84" s="5"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="18">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C85" s="18">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D85" s="18">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E85" s="18">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F85" s="18">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G85" s="18">
+        <v>0.6492</v>
+      </c>
+      <c r="H85" s="18">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I85" s="18"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B86" s="5">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="C86" s="5">
+        <v>0.27850000000000003</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0.45379999999999998</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.64270000000000005</v>
+      </c>
+      <c r="F86" s="5">
         <v>0.64659999999999995</v>
       </c>
-      <c r="F84" s="5">
-        <v>0.64290000000000003</v>
-      </c>
-      <c r="G84" s="5">
-        <v>0.64449999999999996</v>
-      </c>
-      <c r="H84" s="5">
-        <v>0.6502</v>
-      </c>
-      <c r="I84" s="5"/>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B85" s="5">
-        <v>0.60870000000000002</v>
-      </c>
-      <c r="C85" s="5">
-        <v>0.24729999999999999</v>
-      </c>
-      <c r="D85" s="5">
-        <v>0.44729999999999998</v>
-      </c>
-      <c r="E85" s="5">
+      <c r="G86" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F85" s="5">
-        <v>0.59709999999999996</v>
-      </c>
-      <c r="G85" s="5">
-        <v>0.61409999999999998</v>
-      </c>
-      <c r="H85" s="5">
-        <v>0.62350000000000005</v>
-      </c>
-      <c r="I85" s="5"/>
-      <c r="J85" s="23" t="s">
-        <v>125</v>
-      </c>
+      <c r="H86" s="5">
+        <v>0.64910000000000001</v>
+      </c>
+      <c r="I86" s="5"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="B87" s="5">
-        <v>0.61519999999999997</v>
+        <v>0.62519999999999998</v>
       </c>
       <c r="C87" s="5">
-        <v>0.25380000000000003</v>
+        <v>0.27110000000000001</v>
       </c>
       <c r="D87" s="5">
-        <v>0.4516</v>
+        <v>0.45119999999999999</v>
       </c>
       <c r="E87" s="5">
-        <v>0.64549999999999996</v>
+        <v>0.64659999999999995</v>
       </c>
       <c r="F87" s="5">
-        <v>0.64600000000000002</v>
+        <v>0.64290000000000003</v>
       </c>
       <c r="G87" s="5">
-        <v>0.64539999999999997</v>
+        <v>0.64449999999999996</v>
       </c>
       <c r="H87" s="5">
-        <v>0.65049999999999997</v>
+        <v>0.6502</v>
       </c>
       <c r="I87" s="5"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B88" s="18">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="C88" s="18">
-        <v>0.27960000000000002</v>
-      </c>
-      <c r="D88" s="18">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="E88" s="18">
-        <v>0.64729999999999999</v>
-      </c>
-      <c r="F88" s="18">
-        <v>0.64880000000000004</v>
-      </c>
-      <c r="G88" s="18">
-        <v>0.6492</v>
-      </c>
-      <c r="H88" s="18">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="I88" s="18"/>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B89" s="5">
-        <v>0.61080000000000001</v>
-      </c>
-      <c r="C89" s="5">
-        <v>0.2676</v>
-      </c>
-      <c r="D89" s="5">
-        <v>0.4466</v>
-      </c>
-      <c r="E89" s="5">
-        <v>0.64549999999999996</v>
-      </c>
-      <c r="F89" s="5">
-        <v>0.64680000000000004</v>
-      </c>
-      <c r="G89" s="5">
-        <v>0.64810000000000001</v>
-      </c>
-      <c r="H89" s="5">
-        <v>0.65069999999999995</v>
-      </c>
-      <c r="I89" s="5"/>
+      <c r="A88" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="5">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.24729999999999999</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.44729999999999998</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="F88" s="5">
+        <v>0.59709999999999996</v>
+      </c>
+      <c r="G88" s="5">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="H88" s="5">
+        <v>0.62350000000000005</v>
+      </c>
+      <c r="I88" s="5"/>
+      <c r="J88" s="23" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" s="5">
+        <v>0.61519999999999997</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.4516</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F90" s="5">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="G90" s="5">
+        <v>0.64539999999999997</v>
+      </c>
+      <c r="H90" s="5">
+        <v>0.65049999999999997</v>
+      </c>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B91" s="18">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="C91" s="18">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="D91" s="18">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="E91" s="18">
+        <v>0.64729999999999999</v>
+      </c>
+      <c r="F91" s="18">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="G91" s="18">
+        <v>0.6492</v>
+      </c>
+      <c r="H91" s="18">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I91" s="18"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B92" s="5">
+        <v>0.61080000000000001</v>
+      </c>
+      <c r="C92" s="5">
+        <v>0.2676</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.4466</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="F92" s="5">
+        <v>0.64680000000000004</v>
+      </c>
+      <c r="G92" s="5">
+        <v>0.64810000000000001</v>
+      </c>
+      <c r="H92" s="5">
+        <v>0.65069999999999995</v>
+      </c>
+      <c r="I92" s="5"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B93" s="5">
         <v>0.61029999999999995</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C93" s="5">
         <v>0.25590000000000002</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D93" s="5">
         <v>0.43759999999999999</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E93" s="5">
         <v>0.64410000000000001</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F93" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G93" s="5">
         <v>0.64370000000000005</v>
       </c>
-      <c r="H90" s="5">
+      <c r="H93" s="5">
         <v>0.64970000000000006</v>
       </c>
-      <c r="I90" s="5"/>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" s="1" t="s">
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B94" s="5">
         <v>0.61360000000000003</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C94" s="5">
         <v>0.2591</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D94" s="5">
         <v>0.42370000000000002</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E94" s="5">
         <v>0.65590000000000004</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F94" s="5">
         <v>0.64090000000000003</v>
       </c>
-      <c r="G91" s="5">
+      <c r="G94" s="5">
         <v>0.64149999999999996</v>
       </c>
-      <c r="H91" s="5">
+      <c r="H94" s="5">
         <v>0.64249999999999996</v>
       </c>
-      <c r="I91" s="5"/>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="B93" s="1" t="s">
+      <c r="I94" s="5"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="B96" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
-      <c r="B94" s="38" t="s">
+    <row r="97" spans="2:8">
+      <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C94" s="39">
+      <c r="C97" s="5">
         <v>0.22159999999999999</v>
       </c>
-      <c r="D94" s="39">
+      <c r="D97" s="5">
         <v>0.42049999999999998</v>
       </c>
-      <c r="E94" s="39">
+      <c r="E97" s="5">
         <v>0.61409999999999998</v>
       </c>
-      <c r="F94" s="39">
+      <c r="F97" s="5">
         <v>0.62319999999999998</v>
       </c>
-      <c r="G94" s="39">
+      <c r="G97" s="5">
         <v>0.62439999999999996</v>
       </c>
-      <c r="H94" s="39">
+      <c r="H97" s="5">
         <v>0.627</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
-      <c r="B95" s="38" t="s">
+    <row r="98" spans="2:8">
+      <c r="B98" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C95" s="39">
+      <c r="C98" s="5">
         <v>0.23219999999999999</v>
       </c>
-      <c r="D95" s="39">
+      <c r="D98" s="5">
         <v>0.41930000000000001</v>
       </c>
-      <c r="E95" s="39">
+      <c r="E98" s="5">
         <v>0.61980000000000002</v>
       </c>
-      <c r="F95" s="39">
+      <c r="F98" s="5">
         <v>0.61890000000000001</v>
       </c>
-      <c r="G95" s="39">
+      <c r="G98" s="5">
         <v>0.62019999999999997</v>
       </c>
-      <c r="H95" s="39">
+      <c r="H98" s="5">
         <v>0.62670000000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
-      <c r="B96" s="38" t="s">
+    <row r="99" spans="2:8">
+      <c r="B99" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C96" s="39">
+      <c r="C99" s="5">
         <v>0.2432</v>
       </c>
-      <c r="D96" s="39">
+      <c r="D99" s="5">
         <v>0.41320000000000001</v>
       </c>
-      <c r="E96" s="39">
+      <c r="E99" s="5">
         <v>0.59550000000000003</v>
       </c>
-      <c r="F96" s="39">
+      <c r="F99" s="5">
         <v>0.62470000000000003</v>
       </c>
-      <c r="G96" s="39">
+      <c r="G99" s="5">
         <v>0.63060000000000005</v>
       </c>
-      <c r="H96" s="39">
+      <c r="H99" s="5">
         <v>0.63339999999999996</v>
       </c>
     </row>
-    <row r="97" spans="2:8">
-      <c r="B97" s="38" t="s">
+    <row r="100" spans="2:8">
+      <c r="B100" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C97" s="39">
+      <c r="C100" s="5">
         <v>0.2218</v>
       </c>
-      <c r="D97" s="39">
+      <c r="D100" s="5">
         <v>0.40479999999999999</v>
       </c>
-      <c r="E97" s="39">
+      <c r="E100" s="5">
         <v>0.61899999999999999</v>
       </c>
-      <c r="F97" s="39">
+      <c r="F100" s="5">
         <v>0.59419999999999995</v>
       </c>
-      <c r="G97" s="39">
+      <c r="G100" s="5">
         <v>0.59850000000000003</v>
       </c>
-      <c r="H97" s="39">
+      <c r="H100" s="5">
         <v>0.60119999999999996</v>
       </c>
     </row>
-    <row r="98" spans="2:8">
-      <c r="B98" s="38" t="s">
+    <row r="101" spans="2:8">
+      <c r="B101" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C98" s="40" t="s">
+      <c r="C101" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D98" s="40" t="s">
+      <c r="D101" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="E98" s="40" t="s">
+      <c r="E101" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="F98" s="40" t="s">
+      <c r="F101" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G98" s="40" t="s">
+      <c r="G101" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="H98" s="40" t="s">
+      <c r="H101" s="14" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="99" spans="2:8">
-      <c r="B99" s="38" t="s">
+    <row r="102" spans="2:8">
+      <c r="B102" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C99" s="41">
+      <c r="C102" s="6">
         <v>0.27739999999999998</v>
       </c>
-      <c r="D99" s="41">
+      <c r="D102" s="6">
         <v>0.4496</v>
       </c>
-      <c r="E99" s="41">
+      <c r="E102" s="6">
         <v>0.64549999999999996</v>
       </c>
-      <c r="F99" s="41">
+      <c r="F102" s="6">
         <v>0.6421</v>
       </c>
-      <c r="G99" s="41">
+      <c r="G102" s="6">
         <v>0.64549999999999996</v>
       </c>
-      <c r="H99" s="41">
+      <c r="H102" s="6">
         <v>0.64980000000000004</v>
       </c>
     </row>
